--- a/research/traditional_assets/database/data/oman/oman_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_oil_gas_integrated.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1175330612616946</v>
+        <v>0.117395011669802</v>
       </c>
       <c r="C2">
-        <v>9.207328190664398</v>
+        <v>9.11779608345484</v>
       </c>
       <c r="D2">
-        <v>6.017328190664399</v>
+        <v>6.019676083454839</v>
       </c>
       <c r="E2">
-        <v>-0.768</v>
+        <v>-0.6761200000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.09188</v>
       </c>
       <c r="G2">
         <v>3.19</v>
@@ -1445,28 +1445,28 @@
         <v>2.859</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.004621564</v>
       </c>
       <c r="N2">
-        <v>2.859</v>
+        <v>2.854378436</v>
       </c>
       <c r="O2">
-        <v>0.42885</v>
+        <v>0.4281567654</v>
       </c>
       <c r="P2">
-        <v>2.43015</v>
+        <v>2.4262216706</v>
       </c>
       <c r="Q2">
-        <v>2.46115</v>
+        <v>2.457221670600001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1175330612616946</v>
+        <v>0.1181489511816182</v>
       </c>
       <c r="T2">
-        <v>0.934922259086021</v>
+        <v>0.9429493693913049</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>618.6217479623782</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.117395011669802</v>
+        <v>0.1172569620779095</v>
       </c>
       <c r="C3">
-        <v>9.11779608345484</v>
+        <v>9.028265809202423</v>
       </c>
       <c r="D3">
-        <v>6.019676083454839</v>
+        <v>6.022025809202423</v>
       </c>
       <c r="E3">
-        <v>-0.6761200000000001</v>
+        <v>-0.58424</v>
       </c>
       <c r="F3">
-        <v>0.09188</v>
+        <v>0.18376</v>
       </c>
       <c r="G3">
         <v>3.19</v>
@@ -1527,28 +1527,28 @@
         <v>2.859</v>
       </c>
       <c r="M3">
-        <v>0.004621564</v>
+        <v>0.009243128</v>
       </c>
       <c r="N3">
-        <v>2.854378436</v>
+        <v>2.849756872</v>
       </c>
       <c r="O3">
-        <v>0.4281567654</v>
+        <v>0.4274635308</v>
       </c>
       <c r="P3">
-        <v>2.4262216706</v>
+        <v>2.4222933412</v>
       </c>
       <c r="Q3">
-        <v>2.457221670600001</v>
+        <v>2.4532933412</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1181489511816182</v>
+        <v>0.1187774102835811</v>
       </c>
       <c r="T3">
-        <v>0.9429493693913049</v>
+        <v>0.951140298274248</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>618.6217479623782</v>
+        <v>309.310873981189</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1172569620779095</v>
+        <v>0.1171189124860169</v>
       </c>
       <c r="C4">
-        <v>9.028265809202423</v>
+        <v>8.938737370054428</v>
       </c>
       <c r="D4">
-        <v>6.022025809202423</v>
+        <v>6.024377370054427</v>
       </c>
       <c r="E4">
-        <v>-0.58424</v>
+        <v>-0.49236</v>
       </c>
       <c r="F4">
-        <v>0.18376</v>
+        <v>0.27564</v>
       </c>
       <c r="G4">
         <v>3.19</v>
@@ -1609,28 +1609,28 @@
         <v>2.859</v>
       </c>
       <c r="M4">
-        <v>0.009243128</v>
+        <v>0.013864692</v>
       </c>
       <c r="N4">
-        <v>2.849756872</v>
+        <v>2.845135308</v>
       </c>
       <c r="O4">
-        <v>0.4274635308</v>
+        <v>0.4267702962</v>
       </c>
       <c r="P4">
-        <v>2.4222933412</v>
+        <v>2.4183650118</v>
       </c>
       <c r="Q4">
-        <v>2.4532933412</v>
+        <v>2.4493650118</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1187774102835811</v>
+        <v>0.1194188273051721</v>
       </c>
       <c r="T4">
-        <v>0.951140298274248</v>
+        <v>0.9595001122887977</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>309.310873981189</v>
+        <v>206.2072493207927</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1171189124860169</v>
+        <v>0.1169808628941244</v>
       </c>
       <c r="C5">
-        <v>8.938737370054428</v>
+        <v>8.849210768161472</v>
       </c>
       <c r="D5">
-        <v>6.024377370054427</v>
+        <v>6.026730768161473</v>
       </c>
       <c r="E5">
-        <v>-0.49236</v>
+        <v>-0.40048</v>
       </c>
       <c r="F5">
-        <v>0.27564</v>
+        <v>0.36752</v>
       </c>
       <c r="G5">
         <v>3.19</v>
@@ -1691,28 +1691,28 @@
         <v>2.859</v>
       </c>
       <c r="M5">
-        <v>0.013864692</v>
+        <v>0.018486256</v>
       </c>
       <c r="N5">
-        <v>2.845135308</v>
+        <v>2.840513744</v>
       </c>
       <c r="O5">
-        <v>0.4267702962</v>
+        <v>0.4260770616</v>
       </c>
       <c r="P5">
-        <v>2.4183650118</v>
+        <v>2.4144366824</v>
       </c>
       <c r="Q5">
-        <v>2.4493650118</v>
+        <v>2.4454366824</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1194188273051721</v>
+        <v>0.1200736071813796</v>
       </c>
       <c r="T5">
-        <v>0.9595001122887977</v>
+        <v>0.9680340890953175</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>206.2072493207927</v>
+        <v>154.6554369905945</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1169808628941244</v>
+        <v>0.1168428133022319</v>
       </c>
       <c r="C6">
-        <v>8.849210768161472</v>
+        <v>8.759686005677553</v>
       </c>
       <c r="D6">
-        <v>6.026730768161473</v>
+        <v>6.029086005677553</v>
       </c>
       <c r="E6">
-        <v>-0.40048</v>
+        <v>-0.3086</v>
       </c>
       <c r="F6">
-        <v>0.36752</v>
+        <v>0.4594</v>
       </c>
       <c r="G6">
         <v>3.19</v>
@@ -1773,28 +1773,28 @@
         <v>2.859</v>
       </c>
       <c r="M6">
-        <v>0.018486256</v>
+        <v>0.02310782</v>
       </c>
       <c r="N6">
-        <v>2.840513744</v>
+        <v>2.83589218</v>
       </c>
       <c r="O6">
-        <v>0.4260770616</v>
+        <v>0.425383827</v>
       </c>
       <c r="P6">
-        <v>2.4144366824</v>
+        <v>2.410508353</v>
       </c>
       <c r="Q6">
-        <v>2.4454366824</v>
+        <v>2.441508353</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1200736071813796</v>
+        <v>0.1207421718970862</v>
       </c>
       <c r="T6">
-        <v>0.9680340890953175</v>
+        <v>0.9767477285714483</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>154.6554369905945</v>
+        <v>123.7243495924756</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1168428133022319</v>
+        <v>0.1167047637103393</v>
       </c>
       <c r="C7">
-        <v>8.759686005677553</v>
+        <v>8.670163084760027</v>
       </c>
       <c r="D7">
-        <v>6.029086005677553</v>
+        <v>6.031443084760027</v>
       </c>
       <c r="E7">
-        <v>-0.3086</v>
+        <v>-0.2167199999999999</v>
       </c>
       <c r="F7">
-        <v>0.4594</v>
+        <v>0.5512800000000001</v>
       </c>
       <c r="G7">
         <v>3.19</v>
@@ -1855,28 +1855,28 @@
         <v>2.859</v>
       </c>
       <c r="M7">
-        <v>0.02310782</v>
+        <v>0.027729384</v>
       </c>
       <c r="N7">
-        <v>2.83589218</v>
+        <v>2.831270616</v>
       </c>
       <c r="O7">
-        <v>0.425383827</v>
+        <v>0.4246905924</v>
       </c>
       <c r="P7">
-        <v>2.410508353</v>
+        <v>2.4065800236</v>
       </c>
       <c r="Q7">
-        <v>2.441508353</v>
+        <v>2.4375800236</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1207421718970862</v>
+        <v>0.121424961393978</v>
       </c>
       <c r="T7">
-        <v>0.9767477285714483</v>
+        <v>0.9856467646321774</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>123.7243495924756</v>
+        <v>103.1036246603963</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1167047637103393</v>
+        <v>0.1165667141184468</v>
       </c>
       <c r="C8">
-        <v>8.670163084760027</v>
+        <v>8.580642007569628</v>
       </c>
       <c r="D8">
-        <v>6.031443084760027</v>
+        <v>6.033802007569627</v>
       </c>
       <c r="E8">
-        <v>-0.21672</v>
+        <v>-0.1248400000000001</v>
       </c>
       <c r="F8">
-        <v>0.55128</v>
+        <v>0.64316</v>
       </c>
       <c r="G8">
         <v>3.19</v>
@@ -1937,28 +1937,28 @@
         <v>2.859</v>
       </c>
       <c r="M8">
-        <v>0.027729384</v>
+        <v>0.032350948</v>
       </c>
       <c r="N8">
-        <v>2.831270616</v>
+        <v>2.826649052</v>
       </c>
       <c r="O8">
-        <v>0.4246905924</v>
+        <v>0.4239973578</v>
       </c>
       <c r="P8">
-        <v>2.4065800236</v>
+        <v>2.4026516942</v>
       </c>
       <c r="Q8">
-        <v>2.4375800236</v>
+        <v>2.4336516942</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.121424961393978</v>
+        <v>0.1221224345359643</v>
       </c>
       <c r="T8">
-        <v>0.9856467646321774</v>
+        <v>0.9947371778124923</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>103.1036246603963</v>
+        <v>88.37453542319687</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1165667141184468</v>
+        <v>0.1164286645265542</v>
       </c>
       <c r="C9">
-        <v>8.580642007569628</v>
+        <v>8.491122776270467</v>
       </c>
       <c r="D9">
-        <v>6.033802007569627</v>
+        <v>6.036162776270467</v>
       </c>
       <c r="E9">
-        <v>-0.12484</v>
+        <v>-0.03295999999999999</v>
       </c>
       <c r="F9">
-        <v>0.6431600000000001</v>
+        <v>0.73504</v>
       </c>
       <c r="G9">
         <v>3.19</v>
@@ -2019,28 +2019,28 @@
         <v>2.859</v>
       </c>
       <c r="M9">
-        <v>0.032350948</v>
+        <v>0.036972512</v>
       </c>
       <c r="N9">
-        <v>2.826649052</v>
+        <v>2.822027488</v>
       </c>
       <c r="O9">
-        <v>0.4239973578</v>
+        <v>0.4233041231999999</v>
       </c>
       <c r="P9">
-        <v>2.4026516942</v>
+        <v>2.3987233648</v>
       </c>
       <c r="Q9">
-        <v>2.4336516942</v>
+        <v>2.4297233648</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1221224345359643</v>
+        <v>0.122835070137559</v>
       </c>
       <c r="T9">
-        <v>0.9947371778124923</v>
+        <v>1.00402520867064</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>88.37453542319686</v>
+        <v>77.32771849529726</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1164286645265542</v>
+        <v>0.1162906149346617</v>
       </c>
       <c r="C10">
-        <v>8.491122776270467</v>
+        <v>8.401605393030051</v>
       </c>
       <c r="D10">
-        <v>6.036162776270467</v>
+        <v>6.038525393030051</v>
       </c>
       <c r="E10">
-        <v>-0.03295999999999999</v>
+        <v>0.05891999999999997</v>
       </c>
       <c r="F10">
-        <v>0.73504</v>
+        <v>0.82692</v>
       </c>
       <c r="G10">
         <v>3.19</v>
@@ -2101,28 +2101,28 @@
         <v>2.859</v>
       </c>
       <c r="M10">
-        <v>0.036972512</v>
+        <v>0.041594076</v>
       </c>
       <c r="N10">
-        <v>2.822027488</v>
+        <v>2.817405924</v>
       </c>
       <c r="O10">
-        <v>0.4233041231999999</v>
+        <v>0.4226108886</v>
       </c>
       <c r="P10">
-        <v>2.3987233648</v>
+        <v>2.3947950354</v>
       </c>
       <c r="Q10">
-        <v>2.4297233648</v>
+        <v>2.4257950354</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.122835070137559</v>
+        <v>0.1235633680600678</v>
       </c>
       <c r="T10">
-        <v>1.00402520867064</v>
+        <v>1.01351737207512</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>77.32771849529726</v>
+        <v>68.73574977359756</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1162906149346617</v>
+        <v>0.1161525653427692</v>
       </c>
       <c r="C11">
-        <v>8.401605393030051</v>
+        <v>8.312089860019277</v>
       </c>
       <c r="D11">
-        <v>6.038525393030051</v>
+        <v>6.040889860019277</v>
       </c>
       <c r="E11">
-        <v>0.05891999999999997</v>
+        <v>0.1507999999999999</v>
       </c>
       <c r="F11">
-        <v>0.82692</v>
+        <v>0.9188</v>
       </c>
       <c r="G11">
         <v>3.19</v>
@@ -2183,28 +2183,28 @@
         <v>2.859</v>
       </c>
       <c r="M11">
-        <v>0.041594076</v>
+        <v>0.04621564</v>
       </c>
       <c r="N11">
-        <v>2.817405924</v>
+        <v>2.81278436</v>
       </c>
       <c r="O11">
-        <v>0.4226108886</v>
+        <v>0.421917654</v>
       </c>
       <c r="P11">
-        <v>2.3947950354</v>
+        <v>2.390866706</v>
       </c>
       <c r="Q11">
-        <v>2.4257950354</v>
+        <v>2.421866706</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1235633680600678</v>
+        <v>0.1243078503808546</v>
       </c>
       <c r="T11">
-        <v>1.01351737207512</v>
+        <v>1.023220472444145</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>68.73574977359756</v>
+        <v>61.86217479623782</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1161525653427692</v>
+        <v>0.1160145157508766</v>
       </c>
       <c r="C12">
-        <v>8.312089860019277</v>
+        <v>8.222576179412442</v>
       </c>
       <c r="D12">
-        <v>6.040889860019277</v>
+        <v>6.043256179412443</v>
       </c>
       <c r="E12">
-        <v>0.1508</v>
+        <v>0.24268</v>
       </c>
       <c r="F12">
-        <v>0.9188000000000001</v>
+        <v>1.01068</v>
       </c>
       <c r="G12">
         <v>3.19</v>
@@ -2265,28 +2265,28 @@
         <v>2.859</v>
       </c>
       <c r="M12">
-        <v>0.04621564</v>
+        <v>0.050837204</v>
       </c>
       <c r="N12">
-        <v>2.81278436</v>
+        <v>2.808162796</v>
       </c>
       <c r="O12">
-        <v>0.421917654</v>
+        <v>0.4212244194</v>
       </c>
       <c r="P12">
-        <v>2.390866706</v>
+        <v>2.3869383766</v>
       </c>
       <c r="Q12">
-        <v>2.421866706</v>
+        <v>2.4179383766</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1243078503808546</v>
+        <v>0.1250690626414344</v>
       </c>
       <c r="T12">
-        <v>1.023220472444145</v>
+        <v>1.033141620012474</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>61.86217479623781</v>
+        <v>56.23834072385256</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1160145157508766</v>
+        <v>0.1158764661589841</v>
       </c>
       <c r="C13">
-        <v>8.222576179412442</v>
+        <v>8.133064353387256</v>
       </c>
       <c r="D13">
-        <v>6.043256179412443</v>
+        <v>6.045624353387256</v>
       </c>
       <c r="E13">
-        <v>0.24268</v>
+        <v>0.33456</v>
       </c>
       <c r="F13">
-        <v>1.01068</v>
+        <v>1.10256</v>
       </c>
       <c r="G13">
         <v>3.19</v>
@@ -2347,28 +2347,28 @@
         <v>2.859</v>
       </c>
       <c r="M13">
-        <v>0.050837204</v>
+        <v>0.055458768</v>
       </c>
       <c r="N13">
-        <v>2.808162796</v>
+        <v>2.803541232</v>
       </c>
       <c r="O13">
-        <v>0.4212244194</v>
+        <v>0.4205311848</v>
       </c>
       <c r="P13">
-        <v>2.3869383766</v>
+        <v>2.3830100472</v>
       </c>
       <c r="Q13">
-        <v>2.4179383766</v>
+        <v>2.4140100472</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1250690626414344</v>
+        <v>0.1258475751806637</v>
       </c>
       <c r="T13">
-        <v>1.033141620012474</v>
+        <v>1.043288248207355</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>56.23834072385256</v>
+        <v>51.55181233019818</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1158764661589841</v>
+        <v>0.1157384165670915</v>
       </c>
       <c r="C14">
-        <v>8.133064353387256</v>
+        <v>8.043554384124842</v>
       </c>
       <c r="D14">
-        <v>6.045624353387256</v>
+        <v>6.047994384124842</v>
       </c>
       <c r="E14">
-        <v>0.33456</v>
+        <v>0.4264400000000002</v>
       </c>
       <c r="F14">
-        <v>1.10256</v>
+        <v>1.19444</v>
       </c>
       <c r="G14">
         <v>3.19</v>
@@ -2429,28 +2429,28 @@
         <v>2.859</v>
       </c>
       <c r="M14">
-        <v>0.055458768</v>
+        <v>0.06008033200000001</v>
       </c>
       <c r="N14">
-        <v>2.803541232</v>
+        <v>2.798919668</v>
       </c>
       <c r="O14">
-        <v>0.4205311848</v>
+        <v>0.4198379502</v>
       </c>
       <c r="P14">
-        <v>2.3830100472</v>
+        <v>2.3790817178</v>
       </c>
       <c r="Q14">
-        <v>2.4140100472</v>
+        <v>2.4100817178</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1258475751806637</v>
+        <v>0.1266439845598753</v>
       </c>
       <c r="T14">
-        <v>1.043288248207355</v>
+        <v>1.053668132222809</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>51.55181233019818</v>
+        <v>47.58628830479831</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1157384165670915</v>
+        <v>0.115600366975199</v>
       </c>
       <c r="C15">
-        <v>8.043554384124842</v>
+        <v>7.954046273809741</v>
       </c>
       <c r="D15">
-        <v>6.047994384124842</v>
+        <v>6.050366273809741</v>
       </c>
       <c r="E15">
-        <v>0.4264400000000002</v>
+        <v>0.5183200000000001</v>
       </c>
       <c r="F15">
-        <v>1.19444</v>
+        <v>1.28632</v>
       </c>
       <c r="G15">
         <v>3.19</v>
@@ -2511,28 +2511,28 @@
         <v>2.859</v>
       </c>
       <c r="M15">
-        <v>0.06008033200000001</v>
+        <v>0.06470189600000001</v>
       </c>
       <c r="N15">
-        <v>2.798919668</v>
+        <v>2.794298104</v>
       </c>
       <c r="O15">
-        <v>0.4198379502</v>
+        <v>0.4191447156</v>
       </c>
       <c r="P15">
-        <v>2.3790817178</v>
+        <v>2.3751533884</v>
       </c>
       <c r="Q15">
-        <v>2.4100817178</v>
+        <v>2.4061533884</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1266439845598753</v>
+        <v>0.1274589150874407</v>
       </c>
       <c r="T15">
-        <v>1.053668132222809</v>
+        <v>1.064289408889784</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>47.58628830479831</v>
+        <v>44.18726771159843</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.115600366975199</v>
+        <v>0.1154623173833064</v>
       </c>
       <c r="C16">
-        <v>7.954046273809741</v>
+        <v>7.864540024629927</v>
       </c>
       <c r="D16">
-        <v>6.050366273809741</v>
+        <v>6.052740024629927</v>
       </c>
       <c r="E16">
-        <v>0.5183200000000001</v>
+        <v>0.6102000000000003</v>
       </c>
       <c r="F16">
-        <v>1.28632</v>
+        <v>1.3782</v>
       </c>
       <c r="G16">
         <v>3.19</v>
@@ -2593,28 +2593,28 @@
         <v>2.859</v>
       </c>
       <c r="M16">
-        <v>0.06470189600000001</v>
+        <v>0.06932346000000002</v>
       </c>
       <c r="N16">
-        <v>2.794298104</v>
+        <v>2.78967654</v>
       </c>
       <c r="O16">
-        <v>0.4191447156</v>
+        <v>0.418451481</v>
       </c>
       <c r="P16">
-        <v>2.3751533884</v>
+        <v>2.371225059</v>
       </c>
       <c r="Q16">
-        <v>2.4061533884</v>
+        <v>2.402225059</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1274589150874407</v>
+        <v>0.1282930204509488</v>
       </c>
       <c r="T16">
-        <v>1.064289408889784</v>
+        <v>1.075160597948924</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>44.18726771159843</v>
+        <v>41.24144986415853</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1154623173833064</v>
+        <v>0.1153242677914139</v>
       </c>
       <c r="C17">
-        <v>7.864540024629928</v>
+        <v>7.775035638776806</v>
       </c>
       <c r="D17">
-        <v>6.052740024629927</v>
+        <v>6.055115638776806</v>
       </c>
       <c r="E17">
-        <v>0.6102000000000001</v>
+        <v>0.70208</v>
       </c>
       <c r="F17">
-        <v>1.3782</v>
+        <v>1.47008</v>
       </c>
       <c r="G17">
         <v>3.19</v>
@@ -2675,28 +2675,28 @@
         <v>2.859</v>
       </c>
       <c r="M17">
-        <v>0.06932346</v>
+        <v>0.073945024</v>
       </c>
       <c r="N17">
-        <v>2.78967654</v>
+        <v>2.785054976</v>
       </c>
       <c r="O17">
-        <v>0.418451481</v>
+        <v>0.4177582464</v>
       </c>
       <c r="P17">
-        <v>2.371225059</v>
+        <v>2.3672967296</v>
       </c>
       <c r="Q17">
-        <v>2.402225059</v>
+        <v>2.3982967296</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1282930204509488</v>
+        <v>0.1291469854659689</v>
       </c>
       <c r="T17">
-        <v>1.075160597948924</v>
+        <v>1.086290624842805</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>41.24144986415854</v>
+        <v>38.66385924764863</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1153242677914139</v>
+        <v>0.1151862181995214</v>
       </c>
       <c r="C18">
-        <v>7.775035638776806</v>
+        <v>7.685533118445229</v>
       </c>
       <c r="D18">
-        <v>6.055115638776806</v>
+        <v>6.05749311844523</v>
       </c>
       <c r="E18">
-        <v>0.70208</v>
+        <v>0.7939600000000002</v>
       </c>
       <c r="F18">
-        <v>1.47008</v>
+        <v>1.56196</v>
       </c>
       <c r="G18">
         <v>3.19</v>
@@ -2757,28 +2757,28 @@
         <v>2.859</v>
       </c>
       <c r="M18">
-        <v>0.073945024</v>
+        <v>0.07856658800000001</v>
       </c>
       <c r="N18">
-        <v>2.785054976</v>
+        <v>2.780433412</v>
       </c>
       <c r="O18">
-        <v>0.4177582464</v>
+        <v>0.4170650117999999</v>
       </c>
       <c r="P18">
-        <v>2.3672967296</v>
+        <v>2.3633684002</v>
       </c>
       <c r="Q18">
-        <v>2.3982967296</v>
+        <v>2.3943684002</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1291469854659689</v>
+        <v>0.1300215279512306</v>
       </c>
       <c r="T18">
-        <v>1.086290624842805</v>
+        <v>1.097688845155816</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>38.66385924764863</v>
+        <v>36.38951458602224</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1151862181995214</v>
+        <v>0.1150481686076288</v>
       </c>
       <c r="C19">
-        <v>7.685533118445229</v>
+        <v>7.596032465833494</v>
       </c>
       <c r="D19">
-        <v>6.05749311844523</v>
+        <v>6.059872465833494</v>
       </c>
       <c r="E19">
-        <v>0.7939600000000002</v>
+        <v>0.8858400000000002</v>
       </c>
       <c r="F19">
-        <v>1.56196</v>
+        <v>1.65384</v>
       </c>
       <c r="G19">
         <v>3.19</v>
@@ -2839,28 +2839,28 @@
         <v>2.859</v>
       </c>
       <c r="M19">
-        <v>0.07856658800000001</v>
+        <v>0.083188152</v>
       </c>
       <c r="N19">
-        <v>2.780433412</v>
+        <v>2.775811848</v>
       </c>
       <c r="O19">
-        <v>0.4170650117999999</v>
+        <v>0.4163717772</v>
       </c>
       <c r="P19">
-        <v>2.3633684002</v>
+        <v>2.3594400708</v>
       </c>
       <c r="Q19">
-        <v>2.3943684002</v>
+        <v>2.3904400708</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1300215279512306</v>
+        <v>0.1309174007410107</v>
       </c>
       <c r="T19">
-        <v>1.097688845155816</v>
+        <v>1.109365070842315</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>36.38951458602224</v>
+        <v>34.36787488679878</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1150481686076288</v>
+        <v>0.1149101190157363</v>
       </c>
       <c r="C20">
-        <v>7.596032465833495</v>
+        <v>7.506533683143349</v>
       </c>
       <c r="D20">
-        <v>6.059872465833494</v>
+        <v>6.062253683143349</v>
       </c>
       <c r="E20">
-        <v>0.88584</v>
+        <v>0.9777200000000001</v>
       </c>
       <c r="F20">
-        <v>1.65384</v>
+        <v>1.74572</v>
       </c>
       <c r="G20">
         <v>3.19</v>
@@ -2921,28 +2921,28 @@
         <v>2.859</v>
       </c>
       <c r="M20">
-        <v>0.083188152</v>
+        <v>0.08780971600000001</v>
       </c>
       <c r="N20">
-        <v>2.775811848</v>
+        <v>2.771190284</v>
       </c>
       <c r="O20">
-        <v>0.4163717772</v>
+        <v>0.4156785426</v>
       </c>
       <c r="P20">
-        <v>2.3594400708</v>
+        <v>2.3555117414</v>
       </c>
       <c r="Q20">
-        <v>2.3904400708</v>
+        <v>2.3865117414</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1309174007410107</v>
+        <v>0.131835393846588</v>
       </c>
       <c r="T20">
-        <v>1.109365070842315</v>
+        <v>1.121329598397616</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>34.36787488679878</v>
+        <v>32.55903936644094</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1149101190157363</v>
+        <v>0.1147720694238437</v>
       </c>
       <c r="C21">
-        <v>7.506533683143349</v>
+        <v>7.417036772580012</v>
       </c>
       <c r="D21">
-        <v>6.062253683143349</v>
+        <v>6.064636772580013</v>
       </c>
       <c r="E21">
-        <v>0.9777200000000001</v>
+        <v>1.0696</v>
       </c>
       <c r="F21">
-        <v>1.74572</v>
+        <v>1.8376</v>
       </c>
       <c r="G21">
         <v>3.19</v>
@@ -3003,28 +3003,28 @@
         <v>2.859</v>
       </c>
       <c r="M21">
-        <v>0.08780971600000001</v>
+        <v>0.09243128</v>
       </c>
       <c r="N21">
-        <v>2.771190284</v>
+        <v>2.76656872</v>
       </c>
       <c r="O21">
-        <v>0.4156785426</v>
+        <v>0.414985308</v>
       </c>
       <c r="P21">
-        <v>2.3555117414</v>
+        <v>2.351583412</v>
       </c>
       <c r="Q21">
-        <v>2.3865117414</v>
+        <v>2.382583412</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.131835393846588</v>
+        <v>0.1327763367798047</v>
       </c>
       <c r="T21">
-        <v>1.121329598397616</v>
+        <v>1.1335932391418</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>32.55903936644094</v>
+        <v>30.9310873981189</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1147720694238437</v>
+        <v>0.1146340198319512</v>
       </c>
       <c r="C22">
-        <v>7.417036772580012</v>
+        <v>7.327541736352169</v>
       </c>
       <c r="D22">
-        <v>6.064636772580013</v>
+        <v>6.067021736352169</v>
       </c>
       <c r="E22">
-        <v>1.0696</v>
+        <v>1.16148</v>
       </c>
       <c r="F22">
-        <v>1.8376</v>
+        <v>1.92948</v>
       </c>
       <c r="G22">
         <v>3.19</v>
@@ -3085,28 +3085,28 @@
         <v>2.859</v>
       </c>
       <c r="M22">
-        <v>0.09243128</v>
+        <v>0.09705284400000001</v>
       </c>
       <c r="N22">
-        <v>2.76656872</v>
+        <v>2.761947156</v>
       </c>
       <c r="O22">
-        <v>0.414985308</v>
+        <v>0.4142920734</v>
       </c>
       <c r="P22">
-        <v>2.351583412</v>
+        <v>2.3476550826</v>
       </c>
       <c r="Q22">
-        <v>2.382583412</v>
+        <v>2.3786550826</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1327763367798047</v>
+        <v>0.1337411010531028</v>
       </c>
       <c r="T22">
-        <v>1.1335932391418</v>
+        <v>1.146167351803559</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>30.9310873981189</v>
+        <v>29.45817847439896</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1146340198319512</v>
+        <v>0.1144959702400587</v>
       </c>
       <c r="C23">
-        <v>7.327541736352169</v>
+        <v>7.238048576671973</v>
       </c>
       <c r="D23">
-        <v>6.067021736352169</v>
+        <v>6.069408576671973</v>
       </c>
       <c r="E23">
-        <v>1.16148</v>
+        <v>1.25336</v>
       </c>
       <c r="F23">
-        <v>1.92948</v>
+        <v>2.02136</v>
       </c>
       <c r="G23">
         <v>3.19</v>
@@ -3167,28 +3167,28 @@
         <v>2.859</v>
       </c>
       <c r="M23">
-        <v>0.097052844</v>
+        <v>0.101674408</v>
       </c>
       <c r="N23">
-        <v>2.761947156</v>
+        <v>2.757325592</v>
       </c>
       <c r="O23">
-        <v>0.4142920734</v>
+        <v>0.4135988388</v>
       </c>
       <c r="P23">
-        <v>2.3476550826</v>
+        <v>2.3437267532</v>
       </c>
       <c r="Q23">
-        <v>2.3786550826</v>
+        <v>2.3747267532</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1337411010531028</v>
+        <v>0.1347306028718701</v>
       </c>
       <c r="T23">
-        <v>1.146167351803558</v>
+        <v>1.15906387761049</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>29.45817847439896</v>
+        <v>28.11917036192628</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1144959702400587</v>
+        <v>0.1143579206481661</v>
       </c>
       <c r="C24">
-        <v>7.238048576671973</v>
+        <v>7.148557295755071</v>
       </c>
       <c r="D24">
-        <v>6.069408576671973</v>
+        <v>6.071797295755071</v>
       </c>
       <c r="E24">
-        <v>1.25336</v>
+        <v>1.34524</v>
       </c>
       <c r="F24">
-        <v>2.02136</v>
+        <v>2.11324</v>
       </c>
       <c r="G24">
         <v>3.19</v>
@@ -3249,28 +3249,28 @@
         <v>2.859</v>
       </c>
       <c r="M24">
-        <v>0.101674408</v>
+        <v>0.106295972</v>
       </c>
       <c r="N24">
-        <v>2.757325592</v>
+        <v>2.752704028</v>
       </c>
       <c r="O24">
-        <v>0.4135988388</v>
+        <v>0.4129056042</v>
       </c>
       <c r="P24">
-        <v>2.3437267532</v>
+        <v>2.3397984238</v>
       </c>
       <c r="Q24">
-        <v>2.3747267532</v>
+        <v>2.3707984238</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1347306028718701</v>
+        <v>0.1357458060365794</v>
       </c>
       <c r="T24">
-        <v>1.15906387761049</v>
+        <v>1.172295378113706</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>28.11917036192628</v>
+        <v>26.8965977374947</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1143579206481661</v>
+        <v>0.1142198710562736</v>
       </c>
       <c r="C25">
-        <v>7.148557295755071</v>
+        <v>7.059067895820592</v>
       </c>
       <c r="D25">
-        <v>6.071797295755071</v>
+        <v>6.074187895820593</v>
       </c>
       <c r="E25">
-        <v>1.34524</v>
+        <v>1.43712</v>
       </c>
       <c r="F25">
-        <v>2.11324</v>
+        <v>2.20512</v>
       </c>
       <c r="G25">
         <v>3.19</v>
@@ -3331,28 +3331,28 @@
         <v>2.859</v>
       </c>
       <c r="M25">
-        <v>0.106295972</v>
+        <v>0.110917536</v>
       </c>
       <c r="N25">
-        <v>2.752704028</v>
+        <v>2.748082464</v>
       </c>
       <c r="O25">
-        <v>0.4129056042</v>
+        <v>0.4122123696</v>
       </c>
       <c r="P25">
-        <v>2.3397984238</v>
+        <v>2.3358700944</v>
       </c>
       <c r="Q25">
-        <v>2.3707984238</v>
+        <v>2.3668700944</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1357458060365794</v>
+        <v>0.1367877250740442</v>
       </c>
       <c r="T25">
-        <v>1.172295378113706</v>
+        <v>1.185875075998585</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>26.8965977374947</v>
+        <v>25.77590616509908</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1142198710562736</v>
+        <v>0.114081821464381</v>
       </c>
       <c r="C26">
-        <v>7.059067895820593</v>
+        <v>6.969580379091166</v>
       </c>
       <c r="D26">
-        <v>6.074187895820593</v>
+        <v>6.076580379091166</v>
       </c>
       <c r="E26">
-        <v>1.43712</v>
+        <v>1.529</v>
       </c>
       <c r="F26">
-        <v>2.20512</v>
+        <v>2.297</v>
       </c>
       <c r="G26">
         <v>3.19</v>
@@ -3413,28 +3413,28 @@
         <v>2.859</v>
       </c>
       <c r="M26">
-        <v>0.110917536</v>
+        <v>0.1155391</v>
       </c>
       <c r="N26">
-        <v>2.748082464</v>
+        <v>2.7434609</v>
       </c>
       <c r="O26">
-        <v>0.4122123696</v>
+        <v>0.411519135</v>
       </c>
       <c r="P26">
-        <v>2.3358700944</v>
+        <v>2.331941765</v>
       </c>
       <c r="Q26">
-        <v>2.3668700944</v>
+        <v>2.362941765</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1367877250740442</v>
+        <v>0.1378574286191747</v>
       </c>
       <c r="T26">
-        <v>1.185875075998585</v>
+        <v>1.199816899160393</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>25.77590616509909</v>
+        <v>24.74486991849512</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.114081821464381</v>
+        <v>0.1139437718724885</v>
       </c>
       <c r="C27">
-        <v>6.969580379091166</v>
+        <v>6.880094747792921</v>
       </c>
       <c r="D27">
-        <v>6.076580379091166</v>
+        <v>6.078974747792921</v>
       </c>
       <c r="E27">
-        <v>1.529</v>
+        <v>1.62088</v>
       </c>
       <c r="F27">
-        <v>2.297</v>
+        <v>2.38888</v>
       </c>
       <c r="G27">
         <v>3.19</v>
@@ -3495,28 +3495,28 @@
         <v>2.859</v>
       </c>
       <c r="M27">
-        <v>0.1155391</v>
+        <v>0.120160664</v>
       </c>
       <c r="N27">
-        <v>2.7434609</v>
+        <v>2.738839336</v>
       </c>
       <c r="O27">
-        <v>0.411519135</v>
+        <v>0.4108259003999999</v>
       </c>
       <c r="P27">
-        <v>2.331941765</v>
+        <v>2.3280134356</v>
       </c>
       <c r="Q27">
-        <v>2.362941765</v>
+        <v>2.3590134356</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1378574286191747</v>
+        <v>0.1389560430709304</v>
       </c>
       <c r="T27">
-        <v>1.199816899160393</v>
+        <v>1.214135528353603</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>24.74486991849512</v>
+        <v>23.79314415239915</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1139437718724885</v>
+        <v>0.1138057222805959</v>
       </c>
       <c r="C28">
-        <v>6.880094747792921</v>
+        <v>6.790611004155496</v>
       </c>
       <c r="D28">
-        <v>6.078974747792921</v>
+        <v>6.081371004155496</v>
       </c>
       <c r="E28">
-        <v>1.62088</v>
+        <v>1.712760000000001</v>
       </c>
       <c r="F28">
-        <v>2.38888</v>
+        <v>2.480760000000001</v>
       </c>
       <c r="G28">
         <v>3.19</v>
@@ -3577,28 +3577,28 @@
         <v>2.859</v>
       </c>
       <c r="M28">
-        <v>0.120160664</v>
+        <v>0.124782228</v>
       </c>
       <c r="N28">
-        <v>2.738839336</v>
+        <v>2.734217772</v>
       </c>
       <c r="O28">
-        <v>0.4108259003999999</v>
+        <v>0.4101326658</v>
       </c>
       <c r="P28">
-        <v>2.3280134356</v>
+        <v>2.3240851062</v>
       </c>
       <c r="Q28">
-        <v>2.3590134356</v>
+        <v>2.3550851062</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1389560430709304</v>
+        <v>0.1400847565487616</v>
       </c>
       <c r="T28">
-        <v>1.214135528353603</v>
+        <v>1.228846448757585</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>23.79314415239915</v>
+        <v>22.91191659119919</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1138057222805959</v>
+        <v>0.1136676726887034</v>
       </c>
       <c r="C29">
-        <v>6.790611004155496</v>
+        <v>6.701129150412054</v>
       </c>
       <c r="D29">
-        <v>6.081371004155496</v>
+        <v>6.083769150412054</v>
       </c>
       <c r="E29">
-        <v>1.712760000000001</v>
+        <v>1.80464</v>
       </c>
       <c r="F29">
-        <v>2.480760000000001</v>
+        <v>2.57264</v>
       </c>
       <c r="G29">
         <v>3.19</v>
@@ -3659,28 +3659,28 @@
         <v>2.859</v>
       </c>
       <c r="M29">
-        <v>0.124782228</v>
+        <v>0.129403792</v>
       </c>
       <c r="N29">
-        <v>2.734217772</v>
+        <v>2.729596208</v>
       </c>
       <c r="O29">
-        <v>0.4101326658</v>
+        <v>0.4094394312</v>
       </c>
       <c r="P29">
-        <v>2.3240851062</v>
+        <v>2.3201567768</v>
       </c>
       <c r="Q29">
-        <v>2.3550851062</v>
+        <v>2.3511567768</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1400847565487616</v>
+        <v>0.1412448231787548</v>
       </c>
       <c r="T29">
-        <v>1.228846448757585</v>
+        <v>1.243966005839456</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>22.91191659119919</v>
+        <v>22.09363385579922</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1136676726887034</v>
+        <v>0.1135296230968109</v>
       </c>
       <c r="C30">
-        <v>6.701129150412054</v>
+        <v>6.611649188799272</v>
       </c>
       <c r="D30">
-        <v>6.083769150412054</v>
+        <v>6.086169188799273</v>
       </c>
       <c r="E30">
-        <v>1.80464</v>
+        <v>1.89652</v>
       </c>
       <c r="F30">
-        <v>2.57264</v>
+        <v>2.66452</v>
       </c>
       <c r="G30">
         <v>3.19</v>
@@ -3741,28 +3741,28 @@
         <v>2.859</v>
       </c>
       <c r="M30">
-        <v>0.129403792</v>
+        <v>0.134025356</v>
       </c>
       <c r="N30">
-        <v>2.729596208</v>
+        <v>2.724974644</v>
       </c>
       <c r="O30">
-        <v>0.4094394312</v>
+        <v>0.4087461966</v>
       </c>
       <c r="P30">
-        <v>2.3201567768</v>
+        <v>2.3162284474</v>
       </c>
       <c r="Q30">
-        <v>2.3511567768</v>
+        <v>2.3472284474</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1412448231787548</v>
+        <v>0.1424375677419872</v>
       </c>
       <c r="T30">
-        <v>1.243966005839456</v>
+        <v>1.259511465937717</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>22.09363385579922</v>
+        <v>21.3317844124958</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1135296230968109</v>
+        <v>0.1133915735049183</v>
       </c>
       <c r="C31">
-        <v>6.611649188799273</v>
+        <v>6.522171121557366</v>
       </c>
       <c r="D31">
-        <v>6.086169188799273</v>
+        <v>6.088571121557366</v>
       </c>
       <c r="E31">
-        <v>1.89652</v>
+        <v>1.9884</v>
       </c>
       <c r="F31">
-        <v>2.66452</v>
+        <v>2.7564</v>
       </c>
       <c r="G31">
         <v>3.19</v>
@@ -3823,28 +3823,28 @@
         <v>2.859</v>
       </c>
       <c r="M31">
-        <v>0.134025356</v>
+        <v>0.13864692</v>
       </c>
       <c r="N31">
-        <v>2.724974644</v>
+        <v>2.72035308</v>
       </c>
       <c r="O31">
-        <v>0.4087461966</v>
+        <v>0.408052962</v>
       </c>
       <c r="P31">
-        <v>2.3162284474</v>
+        <v>2.312300118</v>
       </c>
       <c r="Q31">
-        <v>2.3472284474</v>
+        <v>2.343300118</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1424375677419872</v>
+        <v>0.1436643907213119</v>
       </c>
       <c r="T31">
-        <v>1.259511465937717</v>
+        <v>1.275501082038786</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>21.3317844124958</v>
+        <v>20.62072493207927</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1133915735049183</v>
+        <v>0.1132535239130258</v>
       </c>
       <c r="C32">
-        <v>6.522171121557366</v>
+        <v>6.432694950930081</v>
       </c>
       <c r="D32">
-        <v>6.088571121557366</v>
+        <v>6.090974950930082</v>
       </c>
       <c r="E32">
-        <v>1.9884</v>
+        <v>2.08028</v>
       </c>
       <c r="F32">
-        <v>2.7564</v>
+        <v>2.84828</v>
       </c>
       <c r="G32">
         <v>3.19</v>
@@ -3905,28 +3905,28 @@
         <v>2.859</v>
       </c>
       <c r="M32">
-        <v>0.13864692</v>
+        <v>0.143268484</v>
       </c>
       <c r="N32">
-        <v>2.72035308</v>
+        <v>2.715731516</v>
       </c>
       <c r="O32">
-        <v>0.408052962</v>
+        <v>0.4073597274</v>
       </c>
       <c r="P32">
-        <v>2.312300118</v>
+        <v>2.3083717886</v>
       </c>
       <c r="Q32">
-        <v>2.343300118</v>
+        <v>2.3393717886</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1436643907213119</v>
+        <v>0.1449267737869939</v>
       </c>
       <c r="T32">
-        <v>1.275501082038786</v>
+        <v>1.291954165273219</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>20.62072493207927</v>
+        <v>19.95554025685091</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1132535239130258</v>
+        <v>0.1131154743211332</v>
       </c>
       <c r="C33">
-        <v>6.432694950930081</v>
+        <v>6.343220679164718</v>
       </c>
       <c r="D33">
-        <v>6.090974950930082</v>
+        <v>6.093380679164718</v>
       </c>
       <c r="E33">
-        <v>2.08028</v>
+        <v>2.17216</v>
       </c>
       <c r="F33">
-        <v>2.84828</v>
+        <v>2.94016</v>
       </c>
       <c r="G33">
         <v>3.19</v>
@@ -3987,28 +3987,28 @@
         <v>2.859</v>
       </c>
       <c r="M33">
-        <v>0.143268484</v>
+        <v>0.147890048</v>
       </c>
       <c r="N33">
-        <v>2.715731516</v>
+        <v>2.711109952</v>
       </c>
       <c r="O33">
-        <v>0.4073597274</v>
+        <v>0.4066664928</v>
       </c>
       <c r="P33">
-        <v>2.3083717886</v>
+        <v>2.3044434592</v>
       </c>
       <c r="Q33">
-        <v>2.3393717886</v>
+        <v>2.3354434592</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1449267737869939</v>
+        <v>0.1462262857663724</v>
       </c>
       <c r="T33">
-        <v>1.291954165273219</v>
+        <v>1.308891162720429</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>19.95554025685091</v>
+        <v>19.33192962382432</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1131154743211332</v>
+        <v>0.1129774247292407</v>
       </c>
       <c r="C34">
-        <v>6.343220679164718</v>
+        <v>6.253748308512121</v>
       </c>
       <c r="D34">
-        <v>6.093380679164718</v>
+        <v>6.095788308512121</v>
       </c>
       <c r="E34">
-        <v>2.17216</v>
+        <v>2.26404</v>
       </c>
       <c r="F34">
-        <v>2.94016</v>
+        <v>3.03204</v>
       </c>
       <c r="G34">
         <v>3.19</v>
@@ -4069,28 +4069,28 @@
         <v>2.859</v>
       </c>
       <c r="M34">
-        <v>0.147890048</v>
+        <v>0.152511612</v>
       </c>
       <c r="N34">
-        <v>2.711109952</v>
+        <v>2.706488388</v>
       </c>
       <c r="O34">
-        <v>0.4066664928</v>
+        <v>0.4059732582</v>
       </c>
       <c r="P34">
-        <v>2.3044434592</v>
+        <v>2.3005151298</v>
       </c>
       <c r="Q34">
-        <v>2.3354434592</v>
+        <v>2.3315151298</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1462262857663724</v>
+        <v>0.1475645891481205</v>
       </c>
       <c r="T34">
-        <v>1.308891162720429</v>
+        <v>1.32633374218099</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>19.33192962382432</v>
+        <v>18.74611357461751</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1129774247292407</v>
+        <v>0.1128393751373482</v>
       </c>
       <c r="C35">
-        <v>6.253748308512121</v>
+        <v>6.164277841226694</v>
       </c>
       <c r="D35">
-        <v>6.095788308512121</v>
+        <v>6.098197841226694</v>
       </c>
       <c r="E35">
-        <v>2.26404</v>
+        <v>2.35592</v>
       </c>
       <c r="F35">
-        <v>3.03204</v>
+        <v>3.12392</v>
       </c>
       <c r="G35">
         <v>3.19</v>
@@ -4151,28 +4151,28 @@
         <v>2.859</v>
       </c>
       <c r="M35">
-        <v>0.152511612</v>
+        <v>0.157133176</v>
       </c>
       <c r="N35">
-        <v>2.706488388</v>
+        <v>2.701866824</v>
       </c>
       <c r="O35">
-        <v>0.4059732582</v>
+        <v>0.4052800236</v>
       </c>
       <c r="P35">
-        <v>2.3005151298</v>
+        <v>2.2965868004</v>
       </c>
       <c r="Q35">
-        <v>2.3315151298</v>
+        <v>2.3275868004</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1475645891481205</v>
+        <v>0.1489434471778003</v>
       </c>
       <c r="T35">
-        <v>1.32633374218099</v>
+        <v>1.344304884655506</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>18.74611357461751</v>
+        <v>18.19475729301112</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1128393751373482</v>
+        <v>0.1127013255454556</v>
       </c>
       <c r="C36">
-        <v>6.164277841226694</v>
+        <v>6.074809279566414</v>
       </c>
       <c r="D36">
-        <v>6.098197841226694</v>
+        <v>6.100609279566414</v>
       </c>
       <c r="E36">
-        <v>2.35592</v>
+        <v>2.447800000000001</v>
       </c>
       <c r="F36">
-        <v>3.12392</v>
+        <v>3.215800000000001</v>
       </c>
       <c r="G36">
         <v>3.19</v>
@@ -4233,28 +4233,28 @@
         <v>2.859</v>
       </c>
       <c r="M36">
-        <v>0.157133176</v>
+        <v>0.16175474</v>
       </c>
       <c r="N36">
-        <v>2.701866824</v>
+        <v>2.69724526</v>
       </c>
       <c r="O36">
-        <v>0.4052800236</v>
+        <v>0.4045867889999999</v>
       </c>
       <c r="P36">
-        <v>2.2965868004</v>
+        <v>2.292658471</v>
       </c>
       <c r="Q36">
-        <v>2.3275868004</v>
+        <v>2.323658471</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1489434471778003</v>
+        <v>0.1503647316083933</v>
       </c>
       <c r="T36">
-        <v>1.344304884655506</v>
+        <v>1.362828985360008</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>18.19475729301112</v>
+        <v>17.67490708463937</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1127013255454556</v>
+        <v>0.1125632759535631</v>
       </c>
       <c r="C37">
-        <v>6.074809279566414</v>
+        <v>5.98534262579282</v>
       </c>
       <c r="D37">
-        <v>6.100609279566414</v>
+        <v>6.10302262579282</v>
       </c>
       <c r="E37">
-        <v>2.447800000000001</v>
+        <v>2.539680000000001</v>
       </c>
       <c r="F37">
-        <v>3.215800000000001</v>
+        <v>3.30768</v>
       </c>
       <c r="G37">
         <v>3.19</v>
@@ -4315,28 +4315,28 @@
         <v>2.859</v>
       </c>
       <c r="M37">
-        <v>0.16175474</v>
+        <v>0.166376304</v>
       </c>
       <c r="N37">
-        <v>2.69724526</v>
+        <v>2.692623696</v>
       </c>
       <c r="O37">
-        <v>0.4045867889999999</v>
+        <v>0.4038935544</v>
       </c>
       <c r="P37">
-        <v>2.292658471</v>
+        <v>2.2887301416</v>
       </c>
       <c r="Q37">
-        <v>2.323658471</v>
+        <v>2.3197301416</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1503647316083933</v>
+        <v>0.1518304311774423</v>
       </c>
       <c r="T37">
-        <v>1.362828985360008</v>
+        <v>1.381931964211525</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>17.67490708463937</v>
+        <v>17.18393744339939</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1125632759535631</v>
+        <v>0.1124252263616705</v>
       </c>
       <c r="C38">
-        <v>5.985342625792821</v>
+        <v>5.89587788217104</v>
       </c>
       <c r="D38">
-        <v>6.10302262579282</v>
+        <v>6.10543788217104</v>
       </c>
       <c r="E38">
-        <v>2.53968</v>
+        <v>2.63156</v>
       </c>
       <c r="F38">
-        <v>3.30768</v>
+        <v>3.39956</v>
       </c>
       <c r="G38">
         <v>3.19</v>
@@ -4397,28 +4397,28 @@
         <v>2.859</v>
       </c>
       <c r="M38">
-        <v>0.166376304</v>
+        <v>0.170997868</v>
       </c>
       <c r="N38">
-        <v>2.692623696</v>
+        <v>2.688002132</v>
       </c>
       <c r="O38">
-        <v>0.4038935544</v>
+        <v>0.4032003198</v>
       </c>
       <c r="P38">
-        <v>2.2887301416</v>
+        <v>2.2848018122</v>
       </c>
       <c r="Q38">
-        <v>2.3197301416</v>
+        <v>2.3158018122</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1518304311774423</v>
+        <v>0.1533426608915405</v>
       </c>
       <c r="T38">
-        <v>1.381931964211525</v>
+        <v>1.401641386836106</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>17.18393744339939</v>
+        <v>16.71950670168589</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1124252263616705</v>
+        <v>0.112287176769778</v>
       </c>
       <c r="C39">
-        <v>5.89587788217104</v>
+        <v>5.806415050969782</v>
       </c>
       <c r="D39">
-        <v>6.10543788217104</v>
+        <v>6.107855050969784</v>
       </c>
       <c r="E39">
-        <v>2.63156</v>
+        <v>2.72344</v>
       </c>
       <c r="F39">
-        <v>3.39956</v>
+        <v>3.49144</v>
       </c>
       <c r="G39">
         <v>3.19</v>
@@ -4479,28 +4479,28 @@
         <v>2.859</v>
       </c>
       <c r="M39">
-        <v>0.170997868</v>
+        <v>0.175619432</v>
       </c>
       <c r="N39">
-        <v>2.688002132</v>
+        <v>2.683380568</v>
       </c>
       <c r="O39">
-        <v>0.4032003198</v>
+        <v>0.4025070852</v>
       </c>
       <c r="P39">
-        <v>2.2848018122</v>
+        <v>2.2808734828</v>
       </c>
       <c r="Q39">
-        <v>2.3158018122</v>
+        <v>2.3118734828</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1533426608915405</v>
+        <v>0.1549036722093193</v>
       </c>
       <c r="T39">
-        <v>1.401641386836106</v>
+        <v>1.421986597287287</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>16.71950670168589</v>
+        <v>16.27951968322047</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.112287176769778</v>
+        <v>0.1121491271778854</v>
       </c>
       <c r="C40">
-        <v>5.806415050969782</v>
+        <v>5.716954134461357</v>
       </c>
       <c r="D40">
-        <v>6.107855050969784</v>
+        <v>6.110274134461358</v>
       </c>
       <c r="E40">
-        <v>2.72344</v>
+        <v>2.815320000000001</v>
       </c>
       <c r="F40">
-        <v>3.49144</v>
+        <v>3.583320000000001</v>
       </c>
       <c r="G40">
         <v>3.19</v>
@@ -4561,28 +4561,28 @@
         <v>2.859</v>
       </c>
       <c r="M40">
-        <v>0.175619432</v>
+        <v>0.180240996</v>
       </c>
       <c r="N40">
-        <v>2.683380568</v>
+        <v>2.678759004</v>
       </c>
       <c r="O40">
-        <v>0.4025070852</v>
+        <v>0.4018138506</v>
       </c>
       <c r="P40">
-        <v>2.2808734828</v>
+        <v>2.2769451534</v>
       </c>
       <c r="Q40">
-        <v>2.3118734828</v>
+        <v>2.3079451534</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1549036722093193</v>
+        <v>0.1565158642260417</v>
       </c>
       <c r="T40">
-        <v>1.421986597287287</v>
+        <v>1.442998863818834</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>16.27951968322047</v>
+        <v>15.86209610159944</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1121491271778854</v>
+        <v>0.1120110775859929</v>
       </c>
       <c r="C41">
-        <v>5.716954134461357</v>
+        <v>5.62749513492167</v>
       </c>
       <c r="D41">
-        <v>6.110274134461358</v>
+        <v>6.11269513492167</v>
       </c>
       <c r="E41">
-        <v>2.815320000000001</v>
+        <v>2.9072</v>
       </c>
       <c r="F41">
-        <v>3.583320000000001</v>
+        <v>3.6752</v>
       </c>
       <c r="G41">
         <v>3.19</v>
@@ -4643,28 +4643,28 @@
         <v>2.859</v>
       </c>
       <c r="M41">
-        <v>0.180240996</v>
+        <v>0.18486256</v>
       </c>
       <c r="N41">
-        <v>2.678759004</v>
+        <v>2.67413744</v>
       </c>
       <c r="O41">
-        <v>0.4018138506</v>
+        <v>0.401120616</v>
       </c>
       <c r="P41">
-        <v>2.2769451534</v>
+        <v>2.273016824</v>
       </c>
       <c r="Q41">
-        <v>2.3079451534</v>
+        <v>2.304016824</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1565158642260417</v>
+        <v>0.1581817959766549</v>
       </c>
       <c r="T41">
-        <v>1.442998863818834</v>
+        <v>1.464711539234766</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>15.86209610159944</v>
+        <v>15.46554369905945</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1120110775859929</v>
+        <v>0.1118730279941004</v>
       </c>
       <c r="C42">
-        <v>5.62749513492167</v>
+        <v>5.538038054630235</v>
       </c>
       <c r="D42">
-        <v>6.11269513492167</v>
+        <v>6.115118054630234</v>
       </c>
       <c r="E42">
-        <v>2.9072</v>
+        <v>2.99908</v>
       </c>
       <c r="F42">
-        <v>3.6752</v>
+        <v>3.76708</v>
       </c>
       <c r="G42">
         <v>3.19</v>
@@ -4725,28 +4725,28 @@
         <v>2.859</v>
       </c>
       <c r="M42">
-        <v>0.18486256</v>
+        <v>0.189484124</v>
       </c>
       <c r="N42">
-        <v>2.67413744</v>
+        <v>2.669515876</v>
       </c>
       <c r="O42">
-        <v>0.401120616</v>
+        <v>0.4004273814</v>
       </c>
       <c r="P42">
-        <v>2.273016824</v>
+        <v>2.2690884946</v>
       </c>
       <c r="Q42">
-        <v>2.304016824</v>
+        <v>2.3000884946</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1581817959766549</v>
+        <v>0.1599041999900006</v>
       </c>
       <c r="T42">
-        <v>1.464711539234766</v>
+        <v>1.487160237546154</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>15.46554369905945</v>
+        <v>15.08833531615556</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1118730279941004</v>
+        <v>0.1117349784022078</v>
       </c>
       <c r="C43">
-        <v>5.538038054630235</v>
+        <v>5.448582895870184</v>
       </c>
       <c r="D43">
-        <v>6.115118054630234</v>
+        <v>6.117542895870185</v>
       </c>
       <c r="E43">
-        <v>2.99908</v>
+        <v>3.090960000000001</v>
       </c>
       <c r="F43">
-        <v>3.76708</v>
+        <v>3.858960000000001</v>
       </c>
       <c r="G43">
         <v>3.19</v>
@@ -4807,28 +4807,28 @@
         <v>2.859</v>
       </c>
       <c r="M43">
-        <v>0.189484124</v>
+        <v>0.194105688</v>
       </c>
       <c r="N43">
-        <v>2.669515876</v>
+        <v>2.664894312</v>
       </c>
       <c r="O43">
-        <v>0.4004273814</v>
+        <v>0.3997341468</v>
       </c>
       <c r="P43">
-        <v>2.2690884946</v>
+        <v>2.2651601652</v>
       </c>
       <c r="Q43">
-        <v>2.3000884946</v>
+        <v>2.2961601652</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1599041999900006</v>
+        <v>0.1616859972451859</v>
       </c>
       <c r="T43">
-        <v>1.487160237546154</v>
+        <v>1.510383028902762</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>15.08833531615556</v>
+        <v>14.72908923719948</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1117349784022078</v>
+        <v>0.1115969288103153</v>
       </c>
       <c r="C44">
-        <v>5.448582895870185</v>
+        <v>5.359129660928271</v>
       </c>
       <c r="D44">
-        <v>6.117542895870185</v>
+        <v>6.119969660928271</v>
       </c>
       <c r="E44">
-        <v>3.09096</v>
+        <v>3.182840000000001</v>
       </c>
       <c r="F44">
-        <v>3.85896</v>
+        <v>3.95084</v>
       </c>
       <c r="G44">
         <v>3.19</v>
@@ -4889,28 +4889,28 @@
         <v>2.859</v>
       </c>
       <c r="M44">
-        <v>0.194105688</v>
+        <v>0.198727252</v>
       </c>
       <c r="N44">
-        <v>2.664894312</v>
+        <v>2.660272748</v>
       </c>
       <c r="O44">
-        <v>0.3997341468</v>
+        <v>0.3990409122</v>
       </c>
       <c r="P44">
-        <v>2.2651601652</v>
+        <v>2.2612318358</v>
       </c>
       <c r="Q44">
-        <v>2.2961601652</v>
+        <v>2.2922318358</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1616859972451859</v>
+        <v>0.1635303137023075</v>
       </c>
       <c r="T44">
-        <v>1.510383028902761</v>
+        <v>1.534420655043812</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>14.72908923719948</v>
+        <v>14.38655227819484</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1115969288103153</v>
+        <v>0.1114588792184227</v>
       </c>
       <c r="C45">
-        <v>5.359129660928271</v>
+        <v>5.269678352094881</v>
       </c>
       <c r="D45">
-        <v>6.119969660928271</v>
+        <v>6.122398352094882</v>
       </c>
       <c r="E45">
-        <v>3.182840000000001</v>
+        <v>3.27472</v>
       </c>
       <c r="F45">
-        <v>3.95084</v>
+        <v>4.04272</v>
       </c>
       <c r="G45">
         <v>3.19</v>
@@ -4971,28 +4971,28 @@
         <v>2.859</v>
       </c>
       <c r="M45">
-        <v>0.198727252</v>
+        <v>0.203348816</v>
       </c>
       <c r="N45">
-        <v>2.660272748</v>
+        <v>2.655651184</v>
       </c>
       <c r="O45">
-        <v>0.3990409122</v>
+        <v>0.3983476775999999</v>
       </c>
       <c r="P45">
-        <v>2.2612318358</v>
+        <v>2.2573035064</v>
       </c>
       <c r="Q45">
-        <v>2.2922318358</v>
+        <v>2.2883035064</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1635303137023075</v>
+        <v>0.1654404986043263</v>
       </c>
       <c r="T45">
-        <v>1.534420655043812</v>
+        <v>1.559316767832756</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>14.38655227819484</v>
+        <v>14.05958518096314</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1114588792184227</v>
+        <v>0.1113208296265302</v>
       </c>
       <c r="C46">
-        <v>5.269678352094881</v>
+        <v>5.180228971664034</v>
       </c>
       <c r="D46">
-        <v>6.122398352094882</v>
+        <v>6.124828971664035</v>
       </c>
       <c r="E46">
-        <v>3.27472</v>
+        <v>3.366600000000001</v>
       </c>
       <c r="F46">
-        <v>4.04272</v>
+        <v>4.134600000000001</v>
       </c>
       <c r="G46">
         <v>3.19</v>
@@ -5053,28 +5053,28 @@
         <v>2.859</v>
       </c>
       <c r="M46">
-        <v>0.203348816</v>
+        <v>0.20797038</v>
       </c>
       <c r="N46">
-        <v>2.655651184</v>
+        <v>2.65102962</v>
       </c>
       <c r="O46">
-        <v>0.3983476775999999</v>
+        <v>0.397654443</v>
       </c>
       <c r="P46">
-        <v>2.2573035064</v>
+        <v>2.253375177</v>
       </c>
       <c r="Q46">
-        <v>2.2883035064</v>
+        <v>2.284375177</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1654404986043263</v>
+        <v>0.1674201447755094</v>
       </c>
       <c r="T46">
-        <v>1.559316767832756</v>
+        <v>1.585118193814026</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>14.05958518096314</v>
+        <v>13.74714995471951</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1113208296265302</v>
+        <v>0.1111827800346376</v>
       </c>
       <c r="C47">
-        <v>5.180228971664034</v>
+        <v>5.090781521933396</v>
       </c>
       <c r="D47">
-        <v>6.124828971664035</v>
+        <v>6.127261521933397</v>
       </c>
       <c r="E47">
-        <v>3.366600000000001</v>
+        <v>3.458480000000001</v>
       </c>
       <c r="F47">
-        <v>4.134600000000001</v>
+        <v>4.22648</v>
       </c>
       <c r="G47">
         <v>3.19</v>
@@ -5135,28 +5135,28 @@
         <v>2.859</v>
       </c>
       <c r="M47">
-        <v>0.20797038</v>
+        <v>0.212591944</v>
       </c>
       <c r="N47">
-        <v>2.65102962</v>
+        <v>2.646408056</v>
       </c>
       <c r="O47">
-        <v>0.397654443</v>
+        <v>0.3969612084</v>
       </c>
       <c r="P47">
-        <v>2.253375177</v>
+        <v>2.2494468476</v>
       </c>
       <c r="Q47">
-        <v>2.284375177</v>
+        <v>2.2804468476</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1674201447755094</v>
+        <v>0.1694731111752549</v>
       </c>
       <c r="T47">
-        <v>1.585118193814026</v>
+        <v>1.611875228164973</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>13.74714995471951</v>
+        <v>13.44829886874735</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1111827800346376</v>
+        <v>0.1110447304427451</v>
       </c>
       <c r="C48">
-        <v>5.090781521933396</v>
+        <v>5.001336005204285</v>
       </c>
       <c r="D48">
-        <v>6.127261521933397</v>
+        <v>6.129696005204285</v>
       </c>
       <c r="E48">
-        <v>3.458480000000001</v>
+        <v>3.55036</v>
       </c>
       <c r="F48">
-        <v>4.22648</v>
+        <v>4.31836</v>
       </c>
       <c r="G48">
         <v>3.19</v>
@@ -5217,28 +5217,28 @@
         <v>2.859</v>
       </c>
       <c r="M48">
-        <v>0.212591944</v>
+        <v>0.217213508</v>
       </c>
       <c r="N48">
-        <v>2.646408056</v>
+        <v>2.641786492</v>
       </c>
       <c r="O48">
-        <v>0.3969612084</v>
+        <v>0.3962679738</v>
       </c>
       <c r="P48">
-        <v>2.2494468476</v>
+        <v>2.2455185182</v>
       </c>
       <c r="Q48">
-        <v>2.2804468476</v>
+        <v>2.2765185182</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1694731111752549</v>
+        <v>0.1716035480051795</v>
       </c>
       <c r="T48">
-        <v>1.611875228164973</v>
+        <v>1.63964196192539</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>13.44829886874735</v>
+        <v>13.16216485026336</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1110447304427451</v>
+        <v>0.1109066808508526</v>
       </c>
       <c r="C49">
-        <v>5.001336005204285</v>
+        <v>4.911892423781674</v>
       </c>
       <c r="D49">
-        <v>6.129696005204285</v>
+        <v>6.132132423781675</v>
       </c>
       <c r="E49">
-        <v>3.55036</v>
+        <v>3.642240000000001</v>
       </c>
       <c r="F49">
-        <v>4.31836</v>
+        <v>4.410240000000001</v>
       </c>
       <c r="G49">
         <v>3.19</v>
@@ -5299,28 +5299,28 @@
         <v>2.859</v>
       </c>
       <c r="M49">
-        <v>0.217213508</v>
+        <v>0.221835072</v>
       </c>
       <c r="N49">
-        <v>2.641786492</v>
+        <v>2.637164928</v>
       </c>
       <c r="O49">
-        <v>0.3962679738</v>
+        <v>0.3955747392</v>
       </c>
       <c r="P49">
-        <v>2.2455185182</v>
+        <v>2.2415901888</v>
       </c>
       <c r="Q49">
-        <v>2.2765185182</v>
+        <v>2.2725901888</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1716035480051795</v>
+        <v>0.173815924713178</v>
       </c>
       <c r="T49">
-        <v>1.63964196192539</v>
+        <v>1.668476646984284</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>13.16216485026336</v>
+        <v>12.88795308254954</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1109066808508526</v>
+        <v>0.11139338125896</v>
       </c>
       <c r="C50">
-        <v>4.911892423781675</v>
+        <v>4.811431324808397</v>
       </c>
       <c r="D50">
-        <v>6.132132423781675</v>
+        <v>6.123551324808398</v>
       </c>
       <c r="E50">
-        <v>3.64224</v>
+        <v>3.734120000000001</v>
       </c>
       <c r="F50">
-        <v>4.41024</v>
+        <v>4.502120000000001</v>
       </c>
       <c r="G50">
         <v>3.19</v>
@@ -5381,45 +5381,45 @@
         <v>2.859</v>
       </c>
       <c r="M50">
-        <v>0.221835072</v>
+        <v>0.233209816</v>
       </c>
       <c r="N50">
-        <v>2.637164928</v>
+        <v>2.625790184</v>
       </c>
       <c r="O50">
-        <v>0.3955747392</v>
+        <v>0.3938685276</v>
       </c>
       <c r="P50">
-        <v>2.2415901888</v>
+        <v>2.2319216564</v>
       </c>
       <c r="Q50">
-        <v>2.2725901888</v>
+        <v>2.2629216564</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.173815924713178</v>
+        <v>0.1761150612920785</v>
       </c>
       <c r="T50">
-        <v>1.668476646984284</v>
+        <v>1.698442104006271</v>
       </c>
       <c r="U50">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V50">
         <v>0.15</v>
       </c>
       <c r="W50">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y50">
-        <v>12.88795308254954</v>
+        <v>12.25934675065307</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.11139338125896</v>
+        <v>0.1112680816670675</v>
       </c>
       <c r="C51">
-        <v>4.811431324808397</v>
+        <v>4.721758207166011</v>
       </c>
       <c r="D51">
-        <v>6.123551324808398</v>
+        <v>6.125758207166012</v>
       </c>
       <c r="E51">
-        <v>3.734120000000001</v>
+        <v>3.826000000000001</v>
       </c>
       <c r="F51">
-        <v>4.502120000000001</v>
+        <v>4.594</v>
       </c>
       <c r="G51">
         <v>3.19</v>
@@ -5463,28 +5463,28 @@
         <v>2.859</v>
       </c>
       <c r="M51">
-        <v>0.233209816</v>
+        <v>0.2379692</v>
       </c>
       <c r="N51">
-        <v>2.625790184</v>
+        <v>2.6210308</v>
       </c>
       <c r="O51">
-        <v>0.3938685276</v>
+        <v>0.39315462</v>
       </c>
       <c r="P51">
-        <v>2.2319216564</v>
+        <v>2.22787618</v>
       </c>
       <c r="Q51">
-        <v>2.2629216564</v>
+        <v>2.25887618</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1761150612920785</v>
+        <v>0.178506163334135</v>
       </c>
       <c r="T51">
-        <v>1.698442104006271</v>
+        <v>1.729606179309139</v>
       </c>
       <c r="U51">
         <v>0.0518</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>12.25934675065307</v>
+        <v>12.01415981564</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1112680816670675</v>
+        <v>0.1111427820751749</v>
       </c>
       <c r="C52">
-        <v>4.721758207166011</v>
+        <v>4.632086680785082</v>
       </c>
       <c r="D52">
-        <v>6.125758207166012</v>
+        <v>6.127966680785081</v>
       </c>
       <c r="E52">
-        <v>3.826000000000001</v>
+        <v>3.91788</v>
       </c>
       <c r="F52">
-        <v>4.594</v>
+        <v>4.68588</v>
       </c>
       <c r="G52">
         <v>3.19</v>
@@ -5545,28 +5545,28 @@
         <v>2.859</v>
       </c>
       <c r="M52">
-        <v>0.2379692</v>
+        <v>0.242728584</v>
       </c>
       <c r="N52">
-        <v>2.6210308</v>
+        <v>2.616271416</v>
       </c>
       <c r="O52">
-        <v>0.39315462</v>
+        <v>0.3924407124</v>
       </c>
       <c r="P52">
-        <v>2.22787618</v>
+        <v>2.2238307036</v>
       </c>
       <c r="Q52">
-        <v>2.25887618</v>
+        <v>2.2548307036</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.178506163334135</v>
+        <v>0.1809948613779081</v>
       </c>
       <c r="T52">
-        <v>1.729606179309139</v>
+        <v>1.762042257685593</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>12.01415981564</v>
+        <v>11.77858805454903</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1111427820751749</v>
+        <v>0.1110174824832824</v>
       </c>
       <c r="C53">
-        <v>4.632086680785082</v>
+        <v>4.542416747387289</v>
       </c>
       <c r="D53">
-        <v>6.127966680785081</v>
+        <v>6.130176747387289</v>
       </c>
       <c r="E53">
-        <v>3.91788</v>
+        <v>4.009760000000001</v>
       </c>
       <c r="F53">
-        <v>4.68588</v>
+        <v>4.777760000000001</v>
       </c>
       <c r="G53">
         <v>3.19</v>
@@ -5627,28 +5627,28 @@
         <v>2.859</v>
       </c>
       <c r="M53">
-        <v>0.242728584</v>
+        <v>0.247487968</v>
       </c>
       <c r="N53">
-        <v>2.616271416</v>
+        <v>2.611512032</v>
       </c>
       <c r="O53">
-        <v>0.3924407124</v>
+        <v>0.3917268047999999</v>
       </c>
       <c r="P53">
-        <v>2.2238307036</v>
+        <v>2.2197852272</v>
       </c>
       <c r="Q53">
-        <v>2.2548307036</v>
+        <v>2.2507852272</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1809948613779081</v>
+        <v>0.183587255173505</v>
       </c>
       <c r="T53">
-        <v>1.762042257685593</v>
+        <v>1.795829839327732</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>11.77858805454903</v>
+        <v>11.5520767458077</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1110174824832824</v>
+        <v>0.1108921828913899</v>
       </c>
       <c r="C54">
-        <v>4.542416747387289</v>
+        <v>4.452748408696792</v>
       </c>
       <c r="D54">
-        <v>6.130176747387289</v>
+        <v>6.132388408696793</v>
       </c>
       <c r="E54">
-        <v>4.009760000000001</v>
+        <v>4.101640000000001</v>
       </c>
       <c r="F54">
-        <v>4.777760000000001</v>
+        <v>4.86964</v>
       </c>
       <c r="G54">
         <v>3.19</v>
@@ -5709,28 +5709,28 @@
         <v>2.859</v>
       </c>
       <c r="M54">
-        <v>0.247487968</v>
+        <v>0.252247352</v>
       </c>
       <c r="N54">
-        <v>2.611512032</v>
+        <v>2.606752648</v>
       </c>
       <c r="O54">
-        <v>0.3917268047999999</v>
+        <v>0.3910128972</v>
       </c>
       <c r="P54">
-        <v>2.2197852272</v>
+        <v>2.2157397508</v>
       </c>
       <c r="Q54">
-        <v>2.2507852272</v>
+        <v>2.2467397508</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.183587255173505</v>
+        <v>0.1862899635987018</v>
       </c>
       <c r="T54">
-        <v>1.795829839327732</v>
+        <v>1.831055190401452</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>11.5520767458077</v>
+        <v>11.33411303362265</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1108921828913899</v>
+        <v>0.1107668832994973</v>
       </c>
       <c r="C55">
-        <v>4.452748408696792</v>
+        <v>4.363081666440242</v>
       </c>
       <c r="D55">
-        <v>6.132388408696793</v>
+        <v>6.134601666440243</v>
       </c>
       <c r="E55">
-        <v>4.101640000000001</v>
+        <v>4.193520000000001</v>
       </c>
       <c r="F55">
-        <v>4.86964</v>
+        <v>4.961520000000001</v>
       </c>
       <c r="G55">
         <v>3.19</v>
@@ -5791,28 +5791,28 @@
         <v>2.859</v>
       </c>
       <c r="M55">
-        <v>0.252247352</v>
+        <v>0.2570067360000001</v>
       </c>
       <c r="N55">
-        <v>2.606752648</v>
+        <v>2.601993264</v>
       </c>
       <c r="O55">
-        <v>0.3910128972</v>
+        <v>0.3902989896</v>
       </c>
       <c r="P55">
-        <v>2.2157397508</v>
+        <v>2.2116942744</v>
       </c>
       <c r="Q55">
-        <v>2.2467397508</v>
+        <v>2.2426942744</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1862899635987018</v>
+        <v>0.1891101810858637</v>
       </c>
       <c r="T55">
-        <v>1.831055190401452</v>
+        <v>1.867812078478377</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>11.33411303362265</v>
+        <v>11.12422205151852</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1107668832994973</v>
+        <v>0.1106415837076048</v>
       </c>
       <c r="C56">
-        <v>4.363081666440242</v>
+        <v>4.273416522346786</v>
       </c>
       <c r="D56">
-        <v>6.134601666440243</v>
+        <v>6.136816522346788</v>
       </c>
       <c r="E56">
-        <v>4.193520000000001</v>
+        <v>4.285400000000001</v>
       </c>
       <c r="F56">
-        <v>4.961520000000001</v>
+        <v>5.053400000000001</v>
       </c>
       <c r="G56">
         <v>3.19</v>
@@ -5873,28 +5873,28 @@
         <v>2.859</v>
       </c>
       <c r="M56">
-        <v>0.2570067360000001</v>
+        <v>0.26176612</v>
       </c>
       <c r="N56">
-        <v>2.601993264</v>
+        <v>2.59723388</v>
       </c>
       <c r="O56">
-        <v>0.3902989896</v>
+        <v>0.389585082</v>
       </c>
       <c r="P56">
-        <v>2.2116942744</v>
+        <v>2.207648798</v>
       </c>
       <c r="Q56">
-        <v>2.2426942744</v>
+        <v>2.238648798</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1891101810858637</v>
+        <v>0.1920557415724551</v>
       </c>
       <c r="T56">
-        <v>1.867812078478377</v>
+        <v>1.906202606025388</v>
       </c>
       <c r="U56">
         <v>0.0518</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>11.12422205151852</v>
+        <v>10.92196346876364</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1106415837076048</v>
+        <v>0.1105162841157122</v>
       </c>
       <c r="C57">
-        <v>4.273416522346786</v>
+        <v>4.183752978148067</v>
       </c>
       <c r="D57">
-        <v>6.136816522346788</v>
+        <v>6.139032978148068</v>
       </c>
       <c r="E57">
-        <v>4.285400000000001</v>
+        <v>4.377280000000001</v>
       </c>
       <c r="F57">
-        <v>5.053400000000001</v>
+        <v>5.145280000000001</v>
       </c>
       <c r="G57">
         <v>3.19</v>
@@ -5955,28 +5955,28 @@
         <v>2.859</v>
       </c>
       <c r="M57">
-        <v>0.26176612</v>
+        <v>0.266525504</v>
       </c>
       <c r="N57">
-        <v>2.59723388</v>
+        <v>2.592474496</v>
       </c>
       <c r="O57">
-        <v>0.389585082</v>
+        <v>0.3888711744</v>
       </c>
       <c r="P57">
-        <v>2.207648798</v>
+        <v>2.2036033216</v>
       </c>
       <c r="Q57">
-        <v>2.238648798</v>
+        <v>2.2346033216</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1920557415724551</v>
+        <v>0.1951351911720733</v>
       </c>
       <c r="T57">
-        <v>1.906202606025388</v>
+        <v>1.946338157551808</v>
       </c>
       <c r="U57">
         <v>0.0518</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>10.92196346876364</v>
+        <v>10.72692840682143</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1105162841157122</v>
+        <v>0.1103909845238197</v>
       </c>
       <c r="C58">
-        <v>4.183752978148067</v>
+        <v>4.094091035578227</v>
       </c>
       <c r="D58">
-        <v>6.139032978148068</v>
+        <v>6.141251035578229</v>
       </c>
       <c r="E58">
-        <v>4.377280000000001</v>
+        <v>4.469160000000001</v>
       </c>
       <c r="F58">
-        <v>5.145280000000001</v>
+        <v>5.237160000000001</v>
       </c>
       <c r="G58">
         <v>3.19</v>
@@ -6037,28 +6037,28 @@
         <v>2.859</v>
       </c>
       <c r="M58">
-        <v>0.266525504</v>
+        <v>0.2712848880000001</v>
       </c>
       <c r="N58">
-        <v>2.592474496</v>
+        <v>2.587715112</v>
       </c>
       <c r="O58">
-        <v>0.3888711744</v>
+        <v>0.3881572668</v>
       </c>
       <c r="P58">
-        <v>2.2036033216</v>
+        <v>2.1995578452</v>
       </c>
       <c r="Q58">
-        <v>2.2346033216</v>
+        <v>2.2305578452</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1951351911720733</v>
+        <v>0.1983578709856272</v>
       </c>
       <c r="T58">
-        <v>1.946338157551808</v>
+        <v>1.988340478916666</v>
       </c>
       <c r="U58">
         <v>0.0518</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>10.72692840682143</v>
+        <v>10.53873668038597</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1103909845238197</v>
+        <v>0.1102656849319271</v>
       </c>
       <c r="C59">
-        <v>4.094091035578227</v>
+        <v>4.004430696373921</v>
       </c>
       <c r="D59">
-        <v>6.141251035578229</v>
+        <v>6.143470696373922</v>
       </c>
       <c r="E59">
-        <v>4.469160000000001</v>
+        <v>4.561040000000001</v>
       </c>
       <c r="F59">
-        <v>5.237160000000001</v>
+        <v>5.329040000000001</v>
       </c>
       <c r="G59">
         <v>3.19</v>
@@ -6119,28 +6119,28 @@
         <v>2.859</v>
       </c>
       <c r="M59">
-        <v>0.2712848880000001</v>
+        <v>0.276044272</v>
       </c>
       <c r="N59">
-        <v>2.587715112</v>
+        <v>2.582955728</v>
       </c>
       <c r="O59">
-        <v>0.3881572668</v>
+        <v>0.3874433592</v>
       </c>
       <c r="P59">
-        <v>2.1995578452</v>
+        <v>2.1955123688</v>
       </c>
       <c r="Q59">
-        <v>2.2305578452</v>
+        <v>2.2265123688</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1983578709856272</v>
+        <v>0.2017340117426837</v>
       </c>
       <c r="T59">
-        <v>1.988340478916666</v>
+        <v>2.032342910822708</v>
       </c>
       <c r="U59">
         <v>0.0518</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>10.53873668038597</v>
+        <v>10.35703432382759</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1102656849319272</v>
+        <v>0.1101403853400346</v>
       </c>
       <c r="C60">
-        <v>4.004430696373922</v>
+        <v>3.914771962274313</v>
       </c>
       <c r="D60">
-        <v>6.143470696373922</v>
+        <v>6.145691962274312</v>
       </c>
       <c r="E60">
-        <v>4.56104</v>
+        <v>4.65292</v>
       </c>
       <c r="F60">
-        <v>5.32904</v>
+        <v>5.42092</v>
       </c>
       <c r="G60">
         <v>3.19</v>
@@ -6201,28 +6201,28 @@
         <v>2.859</v>
       </c>
       <c r="M60">
-        <v>0.276044272</v>
+        <v>0.280803656</v>
       </c>
       <c r="N60">
-        <v>2.582955728</v>
+        <v>2.578196344</v>
       </c>
       <c r="O60">
-        <v>0.3874433592</v>
+        <v>0.3867294516</v>
       </c>
       <c r="P60">
-        <v>2.1955123688</v>
+        <v>2.1914668924</v>
       </c>
       <c r="Q60">
-        <v>2.2265123688</v>
+        <v>2.2224668924</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2017340117426837</v>
+        <v>0.2052748422927673</v>
       </c>
       <c r="T60">
-        <v>2.032342910822707</v>
+        <v>2.078491802821727</v>
       </c>
       <c r="U60">
         <v>0.0518</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>10.35703432382759</v>
+        <v>10.18149136918645</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1101403853400346</v>
+        <v>0.1100150857481421</v>
       </c>
       <c r="C61">
-        <v>3.914771962274313</v>
+        <v>3.825114835021081</v>
       </c>
       <c r="D61">
-        <v>6.145691962274312</v>
+        <v>6.147914835021081</v>
       </c>
       <c r="E61">
-        <v>4.65292</v>
+        <v>4.744800000000001</v>
       </c>
       <c r="F61">
-        <v>5.42092</v>
+        <v>5.5128</v>
       </c>
       <c r="G61">
         <v>3.19</v>
@@ -6283,28 +6283,28 @@
         <v>2.859</v>
       </c>
       <c r="M61">
-        <v>0.280803656</v>
+        <v>0.28556304</v>
       </c>
       <c r="N61">
-        <v>2.578196344</v>
+        <v>2.57343696</v>
       </c>
       <c r="O61">
-        <v>0.3867294516</v>
+        <v>0.386015544</v>
       </c>
       <c r="P61">
-        <v>2.1914668924</v>
+        <v>2.187421416</v>
       </c>
       <c r="Q61">
-        <v>2.2224668924</v>
+        <v>2.218421416</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2052748422927673</v>
+        <v>0.2089927143703551</v>
       </c>
       <c r="T61">
-        <v>2.078491802821727</v>
+        <v>2.126948139420697</v>
       </c>
       <c r="U61">
         <v>0.0518</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>10.18149136918645</v>
+        <v>10.01179984636667</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1100150857481421</v>
+        <v>0.1098897861562495</v>
       </c>
       <c r="C62">
-        <v>3.825114835021081</v>
+        <v>3.735459316358426</v>
       </c>
       <c r="D62">
-        <v>6.147914835021081</v>
+        <v>6.150139316358427</v>
       </c>
       <c r="E62">
-        <v>4.744800000000001</v>
+        <v>4.83668</v>
       </c>
       <c r="F62">
-        <v>5.5128</v>
+        <v>5.60468</v>
       </c>
       <c r="G62">
         <v>3.19</v>
@@ -6365,28 +6365,28 @@
         <v>2.859</v>
       </c>
       <c r="M62">
-        <v>0.28556304</v>
+        <v>0.290322424</v>
       </c>
       <c r="N62">
-        <v>2.57343696</v>
+        <v>2.568677576</v>
       </c>
       <c r="O62">
-        <v>0.386015544</v>
+        <v>0.3853016364</v>
       </c>
       <c r="P62">
-        <v>2.187421416</v>
+        <v>2.1833759396</v>
       </c>
       <c r="Q62">
-        <v>2.218421416</v>
+        <v>2.2143759396</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2089927143703551</v>
+        <v>0.2129012465544859</v>
       </c>
       <c r="T62">
-        <v>2.126948139420697</v>
+        <v>2.177889416358077</v>
       </c>
       <c r="U62">
         <v>0.0518</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>10.01179984636667</v>
+        <v>9.847671980032791</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1098897861562495</v>
+        <v>0.110660386564357</v>
       </c>
       <c r="C63">
-        <v>3.735459316358426</v>
+        <v>3.629924052012677</v>
       </c>
       <c r="D63">
-        <v>6.150139316358427</v>
+        <v>6.136484052012677</v>
       </c>
       <c r="E63">
-        <v>4.83668</v>
+        <v>4.928560000000001</v>
       </c>
       <c r="F63">
-        <v>5.60468</v>
+        <v>5.696560000000001</v>
       </c>
       <c r="G63">
         <v>3.19</v>
@@ -6447,45 +6447,45 @@
         <v>2.859</v>
       </c>
       <c r="M63">
-        <v>0.290322424</v>
+        <v>0.3047659600000001</v>
       </c>
       <c r="N63">
-        <v>2.568677576</v>
+        <v>2.55423404</v>
       </c>
       <c r="O63">
-        <v>0.3853016364</v>
+        <v>0.3831351059999999</v>
       </c>
       <c r="P63">
-        <v>2.1833759396</v>
+        <v>2.171098934</v>
       </c>
       <c r="Q63">
-        <v>2.2143759396</v>
+        <v>2.202098934</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2129012465544859</v>
+        <v>0.2170154909588342</v>
       </c>
       <c r="T63">
-        <v>2.177889416358077</v>
+        <v>2.231511813134266</v>
       </c>
       <c r="U63">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V63">
         <v>0.15</v>
       </c>
       <c r="W63">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>9.847671980032791</v>
+        <v>9.380968924482247</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.110660386564357</v>
+        <v>0.1105495369724644</v>
       </c>
       <c r="C64">
-        <v>3.629924052012677</v>
+        <v>3.540004604000237</v>
       </c>
       <c r="D64">
-        <v>6.136484052012677</v>
+        <v>6.138444604000237</v>
       </c>
       <c r="E64">
-        <v>4.928560000000001</v>
+        <v>5.020440000000001</v>
       </c>
       <c r="F64">
-        <v>5.696560000000001</v>
+        <v>5.78844</v>
       </c>
       <c r="G64">
         <v>3.19</v>
@@ -6529,28 +6529,28 @@
         <v>2.859</v>
       </c>
       <c r="M64">
-        <v>0.3047659600000001</v>
+        <v>0.30968154</v>
       </c>
       <c r="N64">
-        <v>2.55423404</v>
+        <v>2.54931846</v>
       </c>
       <c r="O64">
-        <v>0.3831351059999999</v>
+        <v>0.3823977689999999</v>
       </c>
       <c r="P64">
-        <v>2.171098934</v>
+        <v>2.166920691</v>
       </c>
       <c r="Q64">
-        <v>2.202098934</v>
+        <v>2.197920691</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2170154909588342</v>
+        <v>0.2213521269526066</v>
       </c>
       <c r="T64">
-        <v>2.231511813134266</v>
+        <v>2.288032717844303</v>
       </c>
       <c r="U64">
         <v>0.0535</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>9.380968924482247</v>
+        <v>9.232064655839672</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1105495369724644</v>
+        <v>0.1104386873805719</v>
       </c>
       <c r="C65">
-        <v>3.540004604000237</v>
+        <v>3.450086409145958</v>
       </c>
       <c r="D65">
-        <v>6.138444604000237</v>
+        <v>6.140406409145958</v>
       </c>
       <c r="E65">
-        <v>5.020440000000001</v>
+        <v>5.11232</v>
       </c>
       <c r="F65">
-        <v>5.78844</v>
+        <v>5.88032</v>
       </c>
       <c r="G65">
         <v>3.19</v>
@@ -6611,28 +6611,28 @@
         <v>2.859</v>
       </c>
       <c r="M65">
-        <v>0.30968154</v>
+        <v>0.31459712</v>
       </c>
       <c r="N65">
-        <v>2.54931846</v>
+        <v>2.54440288</v>
       </c>
       <c r="O65">
-        <v>0.3823977689999999</v>
+        <v>0.3816604319999999</v>
       </c>
       <c r="P65">
-        <v>2.166920691</v>
+        <v>2.162742448</v>
       </c>
       <c r="Q65">
-        <v>2.197920691</v>
+        <v>2.193742448</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2213521269526066</v>
+        <v>0.2259296871682553</v>
       </c>
       <c r="T65">
-        <v>2.288032717844303</v>
+        <v>2.347693672816008</v>
       </c>
       <c r="U65">
         <v>0.0535</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>9.232064655839672</v>
+        <v>9.087813645592178</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1104386873805719</v>
+        <v>0.1103278377886794</v>
       </c>
       <c r="C66">
-        <v>3.450086409145958</v>
+        <v>3.360169468651726</v>
       </c>
       <c r="D66">
-        <v>6.140406409145958</v>
+        <v>6.142369468651727</v>
       </c>
       <c r="E66">
-        <v>5.11232</v>
+        <v>5.204200000000001</v>
       </c>
       <c r="F66">
-        <v>5.88032</v>
+        <v>5.972200000000001</v>
       </c>
       <c r="G66">
         <v>3.19</v>
@@ -6693,28 +6693,28 @@
         <v>2.859</v>
       </c>
       <c r="M66">
-        <v>0.31459712</v>
+        <v>0.3195127</v>
       </c>
       <c r="N66">
-        <v>2.54440288</v>
+        <v>2.5394873</v>
       </c>
       <c r="O66">
-        <v>0.3816604319999999</v>
+        <v>0.3809230949999999</v>
       </c>
       <c r="P66">
-        <v>2.162742448</v>
+        <v>2.158564205</v>
       </c>
       <c r="Q66">
-        <v>2.193742448</v>
+        <v>2.189564205</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2259296871682553</v>
+        <v>0.2307688222533696</v>
       </c>
       <c r="T66">
-        <v>2.347693672816008</v>
+        <v>2.410763825214669</v>
       </c>
       <c r="U66">
         <v>0.0535</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>9.087813645592178</v>
+        <v>8.948001127967682</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1103278377886794</v>
+        <v>0.1102169881967868</v>
       </c>
       <c r="C67">
-        <v>3.360169468651726</v>
+        <v>3.270253783720969</v>
       </c>
       <c r="D67">
-        <v>6.142369468651727</v>
+        <v>6.144333783720969</v>
       </c>
       <c r="E67">
-        <v>5.204200000000001</v>
+        <v>5.296080000000001</v>
       </c>
       <c r="F67">
-        <v>5.972200000000001</v>
+        <v>6.064080000000001</v>
       </c>
       <c r="G67">
         <v>3.19</v>
@@ -6775,28 +6775,28 @@
         <v>2.859</v>
       </c>
       <c r="M67">
-        <v>0.3195127</v>
+        <v>0.32442828</v>
       </c>
       <c r="N67">
-        <v>2.5394873</v>
+        <v>2.53457172</v>
       </c>
       <c r="O67">
-        <v>0.3809230949999999</v>
+        <v>0.3801857579999999</v>
       </c>
       <c r="P67">
-        <v>2.158564205</v>
+        <v>2.154385962</v>
       </c>
       <c r="Q67">
-        <v>2.189564205</v>
+        <v>2.185385962</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2307688222533696</v>
+        <v>0.2358926123434907</v>
       </c>
       <c r="T67">
-        <v>2.410763825214669</v>
+        <v>2.477543986577956</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>8.948001127967682</v>
+        <v>8.812425353301506</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1102169881967868</v>
+        <v>0.1101061386048943</v>
       </c>
       <c r="C68">
-        <v>3.270253783720969</v>
+        <v>3.180339355558647</v>
       </c>
       <c r="D68">
-        <v>6.144333783720969</v>
+        <v>6.146299355558647</v>
       </c>
       <c r="E68">
-        <v>5.296080000000001</v>
+        <v>5.387960000000001</v>
       </c>
       <c r="F68">
-        <v>6.064080000000001</v>
+        <v>6.155960000000001</v>
       </c>
       <c r="G68">
         <v>3.19</v>
@@ -6857,28 +6857,28 @@
         <v>2.859</v>
       </c>
       <c r="M68">
-        <v>0.32442828</v>
+        <v>0.32934386</v>
       </c>
       <c r="N68">
-        <v>2.53457172</v>
+        <v>2.52965614</v>
       </c>
       <c r="O68">
-        <v>0.3801857579999999</v>
+        <v>0.379448421</v>
       </c>
       <c r="P68">
-        <v>2.154385962</v>
+        <v>2.150207719</v>
       </c>
       <c r="Q68">
-        <v>2.185385962</v>
+        <v>2.181207719</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2358926123434907</v>
+        <v>0.2413269351663463</v>
       </c>
       <c r="T68">
-        <v>2.477543986577956</v>
+        <v>2.548371430448109</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>8.812425353301506</v>
+        <v>8.680896616685065</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1101061386048943</v>
+        <v>0.1099952890130017</v>
       </c>
       <c r="C69">
-        <v>3.180339355558647</v>
+        <v>3.090426185371267</v>
       </c>
       <c r="D69">
-        <v>6.146299355558647</v>
+        <v>6.148266185371267</v>
       </c>
       <c r="E69">
-        <v>5.387960000000001</v>
+        <v>5.479840000000001</v>
       </c>
       <c r="F69">
-        <v>6.155960000000001</v>
+        <v>6.247840000000001</v>
       </c>
       <c r="G69">
         <v>3.19</v>
@@ -6939,28 +6939,28 @@
         <v>2.859</v>
       </c>
       <c r="M69">
-        <v>0.32934386</v>
+        <v>0.33425944</v>
       </c>
       <c r="N69">
-        <v>2.52965614</v>
+        <v>2.52474056</v>
       </c>
       <c r="O69">
-        <v>0.379448421</v>
+        <v>0.378711084</v>
       </c>
       <c r="P69">
-        <v>2.150207719</v>
+        <v>2.146029476</v>
       </c>
       <c r="Q69">
-        <v>2.181207719</v>
+        <v>2.177029476</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2413269351663463</v>
+        <v>0.2471009031656304</v>
       </c>
       <c r="T69">
-        <v>2.548371430448109</v>
+        <v>2.623625589560147</v>
       </c>
       <c r="U69">
         <v>0.0535</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>8.680896616685065</v>
+        <v>8.553236372322051</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1099952890130017</v>
+        <v>0.1098844394211092</v>
       </c>
       <c r="C70">
-        <v>3.090426185371267</v>
+        <v>3.000514274366881</v>
       </c>
       <c r="D70">
-        <v>6.148266185371267</v>
+        <v>6.150234274366882</v>
       </c>
       <c r="E70">
-        <v>5.479840000000001</v>
+        <v>5.571720000000001</v>
       </c>
       <c r="F70">
-        <v>6.247840000000001</v>
+        <v>6.339720000000001</v>
       </c>
       <c r="G70">
         <v>3.19</v>
@@ -7021,28 +7021,28 @@
         <v>2.859</v>
       </c>
       <c r="M70">
-        <v>0.33425944</v>
+        <v>0.33917502</v>
       </c>
       <c r="N70">
-        <v>2.52474056</v>
+        <v>2.51982498</v>
       </c>
       <c r="O70">
-        <v>0.378711084</v>
+        <v>0.377973747</v>
       </c>
       <c r="P70">
-        <v>2.146029476</v>
+        <v>2.141851233</v>
       </c>
       <c r="Q70">
-        <v>2.177029476</v>
+        <v>2.172851233</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2471009031656304</v>
+        <v>0.2532473852293846</v>
       </c>
       <c r="T70">
-        <v>2.623625589560147</v>
+        <v>2.703734855711671</v>
       </c>
       <c r="U70">
         <v>0.0535</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>8.553236372322051</v>
+        <v>8.429276424897093</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1098844394211092</v>
+        <v>0.1097735898292166</v>
       </c>
       <c r="C71">
-        <v>3.000514274366881</v>
+        <v>2.910603623755087</v>
       </c>
       <c r="D71">
-        <v>6.150234274366882</v>
+        <v>6.152203623755089</v>
       </c>
       <c r="E71">
-        <v>5.571720000000001</v>
+        <v>5.663600000000002</v>
       </c>
       <c r="F71">
-        <v>6.339720000000001</v>
+        <v>6.431600000000001</v>
       </c>
       <c r="G71">
         <v>3.19</v>
@@ -7103,28 +7103,28 @@
         <v>2.859</v>
       </c>
       <c r="M71">
-        <v>0.33917502</v>
+        <v>0.3440906000000001</v>
       </c>
       <c r="N71">
-        <v>2.51982498</v>
+        <v>2.5149094</v>
       </c>
       <c r="O71">
-        <v>0.377973747</v>
+        <v>0.37723641</v>
       </c>
       <c r="P71">
-        <v>2.141851233</v>
+        <v>2.13767299</v>
       </c>
       <c r="Q71">
-        <v>2.172851233</v>
+        <v>2.16867299</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2532473852293846</v>
+        <v>0.2598036327640555</v>
       </c>
       <c r="T71">
-        <v>2.703734855711671</v>
+        <v>2.78918473960663</v>
       </c>
       <c r="U71">
         <v>0.0535</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>8.429276424897093</v>
+        <v>8.308858190255705</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1097735898292166</v>
+        <v>0.1096627402373241</v>
       </c>
       <c r="C72">
-        <v>2.910603623755087</v>
+        <v>2.820694234747034</v>
       </c>
       <c r="D72">
-        <v>6.152203623755089</v>
+        <v>6.154174234747035</v>
       </c>
       <c r="E72">
-        <v>5.663600000000002</v>
+        <v>5.755480000000001</v>
       </c>
       <c r="F72">
-        <v>6.431600000000001</v>
+        <v>6.523480000000001</v>
       </c>
       <c r="G72">
         <v>3.19</v>
@@ -7185,28 +7185,28 @@
         <v>2.859</v>
       </c>
       <c r="M72">
-        <v>0.3440906000000001</v>
+        <v>0.3490061800000001</v>
       </c>
       <c r="N72">
-        <v>2.5149094</v>
+        <v>2.50999382</v>
       </c>
       <c r="O72">
-        <v>0.37723641</v>
+        <v>0.376499073</v>
       </c>
       <c r="P72">
-        <v>2.13767299</v>
+        <v>2.133494747</v>
       </c>
       <c r="Q72">
-        <v>2.16867299</v>
+        <v>2.164494747</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2598036327640555</v>
+        <v>0.2668120353011177</v>
       </c>
       <c r="T72">
-        <v>2.78918473960663</v>
+        <v>2.880527718942621</v>
       </c>
       <c r="U72">
         <v>0.0535</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>8.308858190255705</v>
+        <v>8.191832018561962</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1096627402373241</v>
+        <v>0.1095518906454316</v>
       </c>
       <c r="C73">
-        <v>2.820694234747035</v>
+        <v>2.730786108555422</v>
       </c>
       <c r="D73">
-        <v>6.154174234747035</v>
+        <v>6.156146108555421</v>
       </c>
       <c r="E73">
-        <v>5.75548</v>
+        <v>5.84736</v>
       </c>
       <c r="F73">
-        <v>6.52348</v>
+        <v>6.61536</v>
       </c>
       <c r="G73">
         <v>3.19</v>
@@ -7267,28 +7267,28 @@
         <v>2.859</v>
       </c>
       <c r="M73">
-        <v>0.34900618</v>
+        <v>0.35392176</v>
       </c>
       <c r="N73">
-        <v>2.50999382</v>
+        <v>2.50507824</v>
       </c>
       <c r="O73">
-        <v>0.376499073</v>
+        <v>0.375761736</v>
       </c>
       <c r="P73">
-        <v>2.133494747</v>
+        <v>2.129316504</v>
       </c>
       <c r="Q73">
-        <v>2.164494747</v>
+        <v>2.160316504</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2668120353011176</v>
+        <v>0.2743210380193984</v>
       </c>
       <c r="T73">
-        <v>2.880527718942619</v>
+        <v>2.97839519680261</v>
       </c>
       <c r="U73">
         <v>0.0535</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>8.191832018561964</v>
+        <v>8.078056573859715</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1095518906454316</v>
+        <v>0.109441041053539</v>
       </c>
       <c r="C74">
-        <v>2.730786108555422</v>
+        <v>2.640879246394505</v>
       </c>
       <c r="D74">
-        <v>6.156146108555421</v>
+        <v>6.158119246394505</v>
       </c>
       <c r="E74">
-        <v>5.84736</v>
+        <v>5.939240000000001</v>
       </c>
       <c r="F74">
-        <v>6.61536</v>
+        <v>6.707240000000001</v>
       </c>
       <c r="G74">
         <v>3.19</v>
@@ -7349,28 +7349,28 @@
         <v>2.859</v>
       </c>
       <c r="M74">
-        <v>0.35392176</v>
+        <v>0.35883734</v>
       </c>
       <c r="N74">
-        <v>2.50507824</v>
+        <v>2.50016266</v>
       </c>
       <c r="O74">
-        <v>0.375761736</v>
+        <v>0.375024399</v>
       </c>
       <c r="P74">
-        <v>2.129316504</v>
+        <v>2.125138261</v>
       </c>
       <c r="Q74">
-        <v>2.160316504</v>
+        <v>2.156138261</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2743210380193984</v>
+        <v>0.2823862631612556</v>
       </c>
       <c r="T74">
-        <v>2.97839519680261</v>
+        <v>3.083512117467043</v>
       </c>
       <c r="U74">
         <v>0.0535</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>8.078056573859715</v>
+        <v>7.967398264628759</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.109441041053539</v>
+        <v>0.1093301914616465</v>
       </c>
       <c r="C75">
-        <v>2.640879246394505</v>
+        <v>2.550973649480095</v>
       </c>
       <c r="D75">
-        <v>6.158119246394505</v>
+        <v>6.160093649480096</v>
       </c>
       <c r="E75">
-        <v>5.939240000000001</v>
+        <v>6.03112</v>
       </c>
       <c r="F75">
-        <v>6.707240000000001</v>
+        <v>6.79912</v>
       </c>
       <c r="G75">
         <v>3.19</v>
@@ -7431,28 +7431,28 @@
         <v>2.859</v>
       </c>
       <c r="M75">
-        <v>0.35883734</v>
+        <v>0.36375292</v>
       </c>
       <c r="N75">
-        <v>2.50016266</v>
+        <v>2.49524708</v>
       </c>
       <c r="O75">
-        <v>0.375024399</v>
+        <v>0.374287062</v>
       </c>
       <c r="P75">
-        <v>2.125138261</v>
+        <v>2.120960018</v>
       </c>
       <c r="Q75">
-        <v>2.156138261</v>
+        <v>2.151960018</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2823862631612556</v>
+        <v>0.2910718902371018</v>
       </c>
       <c r="T75">
-        <v>3.083512117467043</v>
+        <v>3.196714955105664</v>
       </c>
       <c r="U75">
         <v>0.0535</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>7.967398264628759</v>
+        <v>7.859730720512154</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1093301914616465</v>
+        <v>0.1092193418697539</v>
       </c>
       <c r="C76">
-        <v>2.550973649480095</v>
+        <v>2.461069319029569</v>
       </c>
       <c r="D76">
-        <v>6.160093649480096</v>
+        <v>6.16206931902957</v>
       </c>
       <c r="E76">
-        <v>6.03112</v>
+        <v>6.123</v>
       </c>
       <c r="F76">
-        <v>6.79912</v>
+        <v>6.891</v>
       </c>
       <c r="G76">
         <v>3.19</v>
@@ -7513,28 +7513,28 @@
         <v>2.859</v>
       </c>
       <c r="M76">
-        <v>0.36375292</v>
+        <v>0.3686685</v>
       </c>
       <c r="N76">
-        <v>2.49524708</v>
+        <v>2.4903315</v>
       </c>
       <c r="O76">
-        <v>0.374287062</v>
+        <v>0.373549725</v>
       </c>
       <c r="P76">
-        <v>2.120960018</v>
+        <v>2.116781775</v>
       </c>
       <c r="Q76">
-        <v>2.151960018</v>
+        <v>2.147781775</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2910718902371018</v>
+        <v>0.3004523674790158</v>
       </c>
       <c r="T76">
-        <v>3.196714955105664</v>
+        <v>3.318974019755375</v>
       </c>
       <c r="U76">
         <v>0.0535</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>7.859730720512154</v>
+        <v>7.754934310905325</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1092193418697539</v>
+        <v>0.1091084922778614</v>
       </c>
       <c r="C77">
-        <v>2.461069319029569</v>
+        <v>2.371166256261858</v>
       </c>
       <c r="D77">
-        <v>6.16206931902957</v>
+        <v>6.164046256261858</v>
       </c>
       <c r="E77">
-        <v>6.123</v>
+        <v>6.214880000000001</v>
       </c>
       <c r="F77">
-        <v>6.891</v>
+        <v>6.982880000000001</v>
       </c>
       <c r="G77">
         <v>3.19</v>
@@ -7595,28 +7595,28 @@
         <v>2.859</v>
       </c>
       <c r="M77">
-        <v>0.3686685</v>
+        <v>0.37358408</v>
       </c>
       <c r="N77">
-        <v>2.4903315</v>
+        <v>2.48541592</v>
       </c>
       <c r="O77">
-        <v>0.373549725</v>
+        <v>0.372812388</v>
       </c>
       <c r="P77">
-        <v>2.116781775</v>
+        <v>2.112603532</v>
       </c>
       <c r="Q77">
-        <v>2.147781775</v>
+        <v>2.143603532</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3004523674790158</v>
+        <v>0.3106145511577558</v>
       </c>
       <c r="T77">
-        <v>3.318974019755375</v>
+        <v>3.451421339792561</v>
       </c>
       <c r="U77">
         <v>0.0535</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>7.754934310905325</v>
+        <v>7.652895701551307</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1091084922778614</v>
+        <v>0.1095212426859689</v>
       </c>
       <c r="C78">
-        <v>2.371166256261858</v>
+        <v>2.271931519929695</v>
       </c>
       <c r="D78">
-        <v>6.164046256261858</v>
+        <v>6.156691519929696</v>
       </c>
       <c r="E78">
-        <v>6.214880000000001</v>
+        <v>6.306760000000001</v>
       </c>
       <c r="F78">
-        <v>6.982880000000001</v>
+        <v>7.07476</v>
       </c>
       <c r="G78">
         <v>3.19</v>
@@ -7677,45 +7677,45 @@
         <v>2.859</v>
       </c>
       <c r="M78">
-        <v>0.37358408</v>
+        <v>0.384159468</v>
       </c>
       <c r="N78">
-        <v>2.48541592</v>
+        <v>2.474840532</v>
       </c>
       <c r="O78">
-        <v>0.372812388</v>
+        <v>0.3712260798</v>
       </c>
       <c r="P78">
-        <v>2.112603532</v>
+        <v>2.1036144522</v>
       </c>
       <c r="Q78">
-        <v>2.143603532</v>
+        <v>2.1346144522</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3106145511577558</v>
+        <v>0.3216604029824733</v>
       </c>
       <c r="T78">
-        <v>3.451421339792561</v>
+        <v>3.59538581809385</v>
       </c>
       <c r="U78">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V78">
         <v>0.15</v>
       </c>
       <c r="W78">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y78">
-        <v>7.652895701551307</v>
+        <v>7.442221884792906</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1095212426859689</v>
+        <v>0.1094171930940763</v>
       </c>
       <c r="C79">
-        <v>2.271931519929695</v>
+        <v>2.181903908662511</v>
       </c>
       <c r="D79">
-        <v>6.156691519929696</v>
+        <v>6.158543908662512</v>
       </c>
       <c r="E79">
-        <v>6.306760000000001</v>
+        <v>6.398640000000001</v>
       </c>
       <c r="F79">
-        <v>7.07476</v>
+        <v>7.166640000000001</v>
       </c>
       <c r="G79">
         <v>3.19</v>
@@ -7759,28 +7759,28 @@
         <v>2.859</v>
       </c>
       <c r="M79">
-        <v>0.384159468</v>
+        <v>0.389148552</v>
       </c>
       <c r="N79">
-        <v>2.474840532</v>
+        <v>2.469851448</v>
       </c>
       <c r="O79">
-        <v>0.3712260798</v>
+        <v>0.3704777172</v>
       </c>
       <c r="P79">
-        <v>2.1036144522</v>
+        <v>2.0993737308</v>
       </c>
       <c r="Q79">
-        <v>2.1346144522</v>
+        <v>2.1303737308</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3216604029824733</v>
+        <v>0.3337104231548923</v>
       </c>
       <c r="T79">
-        <v>3.59538581809385</v>
+        <v>3.752437976240711</v>
       </c>
       <c r="U79">
         <v>0.0543</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>7.442221884792906</v>
+        <v>7.346808783705817</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1094171930940763</v>
+        <v>0.1093131435021838</v>
       </c>
       <c r="C80">
-        <v>2.181903908662511</v>
+        <v>2.091877412402217</v>
       </c>
       <c r="D80">
-        <v>6.158543908662512</v>
+        <v>6.160397412402219</v>
       </c>
       <c r="E80">
-        <v>6.398640000000001</v>
+        <v>6.490520000000001</v>
       </c>
       <c r="F80">
-        <v>7.166640000000001</v>
+        <v>7.258520000000001</v>
       </c>
       <c r="G80">
         <v>3.19</v>
@@ -7841,28 +7841,28 @@
         <v>2.859</v>
       </c>
       <c r="M80">
-        <v>0.389148552</v>
+        <v>0.3941376360000001</v>
       </c>
       <c r="N80">
-        <v>2.469851448</v>
+        <v>2.464862364</v>
       </c>
       <c r="O80">
-        <v>0.3704777172</v>
+        <v>0.3697293546</v>
       </c>
       <c r="P80">
-        <v>2.0993737308</v>
+        <v>2.0951330094</v>
       </c>
       <c r="Q80">
-        <v>2.1303737308</v>
+        <v>2.1261330094</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3337104231548923</v>
+        <v>0.3469080642961132</v>
       </c>
       <c r="T80">
-        <v>3.752437976240711</v>
+        <v>3.924447482782512</v>
       </c>
       <c r="U80">
         <v>0.0543</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>7.346808783705817</v>
+        <v>7.253811204165237</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1093131435021838</v>
+        <v>0.1092090939102912</v>
       </c>
       <c r="C81">
-        <v>2.091877412402217</v>
+        <v>2.001852032155851</v>
       </c>
       <c r="D81">
-        <v>6.160397412402219</v>
+        <v>6.162252032155851</v>
       </c>
       <c r="E81">
-        <v>6.490520000000001</v>
+        <v>6.582400000000001</v>
       </c>
       <c r="F81">
-        <v>7.258520000000001</v>
+        <v>7.3504</v>
       </c>
       <c r="G81">
         <v>3.19</v>
@@ -7923,28 +7923,28 @@
         <v>2.859</v>
       </c>
       <c r="M81">
-        <v>0.3941376360000001</v>
+        <v>0.39912672</v>
       </c>
       <c r="N81">
-        <v>2.464862364</v>
+        <v>2.45987328</v>
       </c>
       <c r="O81">
-        <v>0.3697293546</v>
+        <v>0.368980992</v>
       </c>
       <c r="P81">
-        <v>2.0951330094</v>
+        <v>2.090892288</v>
       </c>
       <c r="Q81">
-        <v>2.1261330094</v>
+        <v>2.121892288</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3469080642961132</v>
+        <v>0.3614254695514562</v>
       </c>
       <c r="T81">
-        <v>3.924447482782512</v>
+        <v>4.113657939978493</v>
       </c>
       <c r="U81">
         <v>0.0543</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>7.253811204165237</v>
+        <v>7.163138564113171</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1092090939102912</v>
+        <v>0.1091050443183987</v>
       </c>
       <c r="C82">
-        <v>2.001852032155851</v>
+        <v>1.911827768931656</v>
       </c>
       <c r="D82">
-        <v>6.162252032155851</v>
+        <v>6.164107768931657</v>
       </c>
       <c r="E82">
-        <v>6.582400000000001</v>
+        <v>6.674280000000001</v>
       </c>
       <c r="F82">
-        <v>7.3504</v>
+        <v>7.442280000000001</v>
       </c>
       <c r="G82">
         <v>3.19</v>
@@ -8005,28 +8005,28 @@
         <v>2.859</v>
       </c>
       <c r="M82">
-        <v>0.39912672</v>
+        <v>0.4041158040000001</v>
       </c>
       <c r="N82">
-        <v>2.45987328</v>
+        <v>2.454884196</v>
       </c>
       <c r="O82">
-        <v>0.368980992</v>
+        <v>0.3682326294</v>
       </c>
       <c r="P82">
-        <v>2.090892288</v>
+        <v>2.0866515666</v>
       </c>
       <c r="Q82">
-        <v>2.121892288</v>
+        <v>2.1176515666</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3614254695514562</v>
+        <v>0.3774710227284142</v>
       </c>
       <c r="T82">
-        <v>4.113657939978493</v>
+        <v>4.32278528740563</v>
       </c>
       <c r="U82">
         <v>0.0543</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>7.163138564113171</v>
+        <v>7.074704754679675</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1091050443183987</v>
+        <v>0.1090009947265061</v>
       </c>
       <c r="C83">
-        <v>1.911827768931656</v>
+        <v>1.821804623739101</v>
       </c>
       <c r="D83">
-        <v>6.164107768931657</v>
+        <v>6.165964623739101</v>
       </c>
       <c r="E83">
-        <v>6.674280000000001</v>
+        <v>6.766160000000001</v>
       </c>
       <c r="F83">
-        <v>7.442280000000001</v>
+        <v>7.534160000000001</v>
       </c>
       <c r="G83">
         <v>3.19</v>
@@ -8087,28 +8087,28 @@
         <v>2.859</v>
       </c>
       <c r="M83">
-        <v>0.4041158040000001</v>
+        <v>0.4091048880000001</v>
       </c>
       <c r="N83">
-        <v>2.454884196</v>
+        <v>2.449895112</v>
       </c>
       <c r="O83">
-        <v>0.3682326294</v>
+        <v>0.3674842668</v>
       </c>
       <c r="P83">
-        <v>2.0866515666</v>
+        <v>2.0824108452</v>
       </c>
       <c r="Q83">
-        <v>2.1176515666</v>
+        <v>2.1134108452</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3774710227284142</v>
+        <v>0.3952994151472564</v>
       </c>
       <c r="T83">
-        <v>4.32278528740563</v>
+        <v>4.555149006769114</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>7.074704754679675</v>
+        <v>6.988427867427484</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1090009947265061</v>
+        <v>0.1088969451346136</v>
       </c>
       <c r="C84">
-        <v>1.821804623739101</v>
+        <v>1.731782597588863</v>
       </c>
       <c r="D84">
-        <v>6.165964623739101</v>
+        <v>6.167822597588865</v>
       </c>
       <c r="E84">
-        <v>6.766160000000001</v>
+        <v>6.858040000000002</v>
       </c>
       <c r="F84">
-        <v>7.534160000000001</v>
+        <v>7.626040000000001</v>
       </c>
       <c r="G84">
         <v>3.19</v>
@@ -8169,28 +8169,28 @@
         <v>2.859</v>
       </c>
       <c r="M84">
-        <v>0.4091048880000001</v>
+        <v>0.4140939720000001</v>
       </c>
       <c r="N84">
-        <v>2.449895112</v>
+        <v>2.444906028</v>
       </c>
       <c r="O84">
-        <v>0.3674842668</v>
+        <v>0.3667359042</v>
       </c>
       <c r="P84">
-        <v>2.0824108452</v>
+        <v>2.0781701238</v>
       </c>
       <c r="Q84">
-        <v>2.1134108452</v>
+        <v>2.1091701238</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3952994151472564</v>
+        <v>0.4152252654977272</v>
       </c>
       <c r="T84">
-        <v>4.555149006769114</v>
+        <v>4.81484963429301</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>6.988427867427484</v>
+        <v>6.9042299413139</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1088969451346136</v>
+        <v>0.1087928955427211</v>
       </c>
       <c r="C85">
-        <v>1.731782597588863</v>
+        <v>1.641761691492844</v>
       </c>
       <c r="D85">
-        <v>6.167822597588865</v>
+        <v>6.169681691492845</v>
       </c>
       <c r="E85">
-        <v>6.858040000000002</v>
+        <v>6.949920000000001</v>
       </c>
       <c r="F85">
-        <v>7.626040000000001</v>
+        <v>7.717920000000001</v>
       </c>
       <c r="G85">
         <v>3.19</v>
@@ -8251,28 +8251,28 @@
         <v>2.859</v>
       </c>
       <c r="M85">
-        <v>0.4140939720000001</v>
+        <v>0.4190830560000001</v>
       </c>
       <c r="N85">
-        <v>2.444906028</v>
+        <v>2.439916944</v>
       </c>
       <c r="O85">
-        <v>0.3667359042</v>
+        <v>0.3659875416</v>
       </c>
       <c r="P85">
-        <v>2.0781701238</v>
+        <v>2.0739294024</v>
       </c>
       <c r="Q85">
-        <v>2.1091701238</v>
+        <v>2.1049294024</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4152252654977272</v>
+        <v>0.4376418471420069</v>
       </c>
       <c r="T85">
-        <v>4.81484963429301</v>
+        <v>5.107012840257393</v>
       </c>
       <c r="U85">
         <v>0.0543</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>6.9042299413139</v>
+        <v>6.82203672772683</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1087928955427211</v>
+        <v>0.1086888459508285</v>
       </c>
       <c r="C86">
-        <v>1.641761691492845</v>
+        <v>1.551741906464163</v>
       </c>
       <c r="D86">
-        <v>6.169681691492845</v>
+        <v>6.171541906464164</v>
       </c>
       <c r="E86">
-        <v>6.949920000000001</v>
+        <v>7.0418</v>
       </c>
       <c r="F86">
-        <v>7.71792</v>
+        <v>7.8098</v>
       </c>
       <c r="G86">
         <v>3.19</v>
@@ -8333,28 +8333,28 @@
         <v>2.859</v>
       </c>
       <c r="M86">
-        <v>0.419083056</v>
+        <v>0.42407214</v>
       </c>
       <c r="N86">
-        <v>2.439916944</v>
+        <v>2.43492786</v>
       </c>
       <c r="O86">
-        <v>0.3659875416</v>
+        <v>0.365239179</v>
       </c>
       <c r="P86">
-        <v>2.0739294024</v>
+        <v>2.069688681</v>
       </c>
       <c r="Q86">
-        <v>2.1049294024</v>
+        <v>2.100688681</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4376418471420066</v>
+        <v>0.4630473063388568</v>
       </c>
       <c r="T86">
-        <v>5.107012840257389</v>
+        <v>5.438131140350356</v>
       </c>
       <c r="U86">
         <v>0.0543</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>6.822036727726831</v>
+        <v>6.741777472106516</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1086888459508285</v>
+        <v>0.108584796358936</v>
       </c>
       <c r="C87">
-        <v>1.551741906464163</v>
+        <v>1.461723243517159</v>
       </c>
       <c r="D87">
-        <v>6.171541906464164</v>
+        <v>6.173403243517161</v>
       </c>
       <c r="E87">
-        <v>7.0418</v>
+        <v>7.133680000000001</v>
       </c>
       <c r="F87">
-        <v>7.8098</v>
+        <v>7.901680000000001</v>
       </c>
       <c r="G87">
         <v>3.19</v>
@@ -8415,28 +8415,28 @@
         <v>2.859</v>
       </c>
       <c r="M87">
-        <v>0.42407214</v>
+        <v>0.429061224</v>
       </c>
       <c r="N87">
-        <v>2.43492786</v>
+        <v>2.429938776</v>
       </c>
       <c r="O87">
-        <v>0.365239179</v>
+        <v>0.3644908164</v>
       </c>
       <c r="P87">
-        <v>2.069688681</v>
+        <v>2.0654479596</v>
       </c>
       <c r="Q87">
-        <v>2.100688681</v>
+        <v>2.0964479596</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4630473063388568</v>
+        <v>0.4920821168495426</v>
       </c>
       <c r="T87">
-        <v>5.438131140350356</v>
+        <v>5.816552054742315</v>
       </c>
       <c r="U87">
         <v>0.0543</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>6.741777472106516</v>
+        <v>6.66338471080295</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.108584796358936</v>
+        <v>0.1084807467670434</v>
       </c>
       <c r="C88">
-        <v>1.461723243517159</v>
+        <v>1.371705703667404</v>
       </c>
       <c r="D88">
-        <v>6.173403243517161</v>
+        <v>6.175265703667405</v>
       </c>
       <c r="E88">
-        <v>7.133680000000001</v>
+        <v>7.225560000000001</v>
       </c>
       <c r="F88">
-        <v>7.901680000000001</v>
+        <v>7.99356</v>
       </c>
       <c r="G88">
         <v>3.19</v>
@@ -8497,28 +8497,28 @@
         <v>2.859</v>
       </c>
       <c r="M88">
-        <v>0.429061224</v>
+        <v>0.4340503080000001</v>
       </c>
       <c r="N88">
-        <v>2.429938776</v>
+        <v>2.424949692</v>
       </c>
       <c r="O88">
-        <v>0.3644908164</v>
+        <v>0.3637424538</v>
       </c>
       <c r="P88">
-        <v>2.0654479596</v>
+        <v>2.0612072382</v>
       </c>
       <c r="Q88">
-        <v>2.0964479596</v>
+        <v>2.0922072382</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4920821168495426</v>
+        <v>0.5255838212849494</v>
       </c>
       <c r="T88">
-        <v>5.816552054742315</v>
+        <v>6.253191571348425</v>
       </c>
       <c r="U88">
         <v>0.0543</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>6.66338471080295</v>
+        <v>6.586794081943145</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1084807467670434</v>
+        <v>0.1083766971751509</v>
       </c>
       <c r="C89">
-        <v>1.371705703667404</v>
+        <v>1.281689287931682</v>
       </c>
       <c r="D89">
-        <v>6.175265703667405</v>
+        <v>6.177129287931683</v>
       </c>
       <c r="E89">
-        <v>7.225560000000001</v>
+        <v>7.31744</v>
       </c>
       <c r="F89">
-        <v>7.99356</v>
+        <v>8.08544</v>
       </c>
       <c r="G89">
         <v>3.19</v>
@@ -8579,28 +8579,28 @@
         <v>2.859</v>
       </c>
       <c r="M89">
-        <v>0.4340503080000001</v>
+        <v>0.439039392</v>
       </c>
       <c r="N89">
-        <v>2.424949692</v>
+        <v>2.419960608</v>
       </c>
       <c r="O89">
-        <v>0.3637424538</v>
+        <v>0.3629940912</v>
       </c>
       <c r="P89">
-        <v>2.0612072382</v>
+        <v>2.0569665168</v>
       </c>
       <c r="Q89">
-        <v>2.0922072382</v>
+        <v>2.0879665168</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5255838212849494</v>
+        <v>0.5646691431262574</v>
       </c>
       <c r="T89">
-        <v>6.253191571348425</v>
+        <v>6.762604340722219</v>
       </c>
       <c r="U89">
         <v>0.0543</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>6.586794081943145</v>
+        <v>6.511944149193792</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1083766971751509</v>
+        <v>0.1082726475832583</v>
       </c>
       <c r="C90">
-        <v>1.281689287931682</v>
+        <v>1.191673997328019</v>
       </c>
       <c r="D90">
-        <v>6.177129287931683</v>
+        <v>6.178993997328019</v>
       </c>
       <c r="E90">
-        <v>7.31744</v>
+        <v>7.40932</v>
       </c>
       <c r="F90">
-        <v>8.08544</v>
+        <v>8.17732</v>
       </c>
       <c r="G90">
         <v>3.19</v>
@@ -8661,28 +8661,28 @@
         <v>2.859</v>
       </c>
       <c r="M90">
-        <v>0.439039392</v>
+        <v>0.444028476</v>
       </c>
       <c r="N90">
-        <v>2.419960608</v>
+        <v>2.414971524</v>
       </c>
       <c r="O90">
-        <v>0.3629940912</v>
+        <v>0.3622457286</v>
       </c>
       <c r="P90">
-        <v>2.0569665168</v>
+        <v>2.0527257954</v>
       </c>
       <c r="Q90">
-        <v>2.0879665168</v>
+        <v>2.0837257954</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5646691431262574</v>
+        <v>0.6108608871205304</v>
       </c>
       <c r="T90">
-        <v>6.762604340722219</v>
+        <v>7.364637613618521</v>
       </c>
       <c r="U90">
         <v>0.0543</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>6.511944149193792</v>
+        <v>6.438776237405098</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1082726475832583</v>
+        <v>0.1081685979913658</v>
       </c>
       <c r="C91">
-        <v>1.191673997328019</v>
+        <v>1.101659832875658</v>
       </c>
       <c r="D91">
-        <v>6.178993997328019</v>
+        <v>6.180859832875659</v>
       </c>
       <c r="E91">
-        <v>7.40932</v>
+        <v>7.501200000000002</v>
       </c>
       <c r="F91">
-        <v>8.17732</v>
+        <v>8.269200000000001</v>
       </c>
       <c r="G91">
         <v>3.19</v>
@@ -8743,28 +8743,28 @@
         <v>2.859</v>
       </c>
       <c r="M91">
-        <v>0.444028476</v>
+        <v>0.4490175600000001</v>
       </c>
       <c r="N91">
-        <v>2.414971524</v>
+        <v>2.40998244</v>
       </c>
       <c r="O91">
-        <v>0.3622457286</v>
+        <v>0.361497366</v>
       </c>
       <c r="P91">
-        <v>2.0527257954</v>
+        <v>2.048485074</v>
       </c>
       <c r="Q91">
-        <v>2.0837257954</v>
+        <v>2.079485074</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6108608871205304</v>
+        <v>0.6662909799136583</v>
       </c>
       <c r="T91">
-        <v>7.364637613618521</v>
+        <v>8.087077541094084</v>
       </c>
       <c r="U91">
         <v>0.0543</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>6.438776237405098</v>
+        <v>6.367234279211707</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1081685979913658</v>
+        <v>0.1080645483994733</v>
       </c>
       <c r="C92">
-        <v>1.101659832875658</v>
+        <v>1.011646795595084</v>
       </c>
       <c r="D92">
-        <v>6.180859832875659</v>
+        <v>6.182726795595086</v>
       </c>
       <c r="E92">
-        <v>7.501200000000002</v>
+        <v>7.593080000000001</v>
       </c>
       <c r="F92">
-        <v>8.269200000000001</v>
+        <v>8.361080000000001</v>
       </c>
       <c r="G92">
         <v>3.19</v>
@@ -8825,28 +8825,28 @@
         <v>2.859</v>
       </c>
       <c r="M92">
-        <v>0.4490175600000001</v>
+        <v>0.4540066440000001</v>
       </c>
       <c r="N92">
-        <v>2.40998244</v>
+        <v>2.404993356</v>
       </c>
       <c r="O92">
-        <v>0.361497366</v>
+        <v>0.3607490034</v>
       </c>
       <c r="P92">
-        <v>2.048485074</v>
+        <v>2.0442443526</v>
       </c>
       <c r="Q92">
-        <v>2.079485074</v>
+        <v>2.0752443526</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6662909799136583</v>
+        <v>0.7340388711052587</v>
       </c>
       <c r="T92">
-        <v>8.087077541094084</v>
+        <v>8.970059674675326</v>
       </c>
       <c r="U92">
         <v>0.0543</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>6.367234279211707</v>
+        <v>6.297264671747842</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1080645483994733</v>
+        <v>0.1079604988075807</v>
       </c>
       <c r="C93">
-        <v>1.011646795595084</v>
+        <v>0.9216348865080111</v>
       </c>
       <c r="D93">
-        <v>6.182726795595086</v>
+        <v>6.184594886508012</v>
       </c>
       <c r="E93">
-        <v>7.593080000000001</v>
+        <v>7.684960000000001</v>
       </c>
       <c r="F93">
-        <v>8.361080000000001</v>
+        <v>8.452960000000001</v>
       </c>
       <c r="G93">
         <v>3.19</v>
@@ -8907,28 +8907,28 @@
         <v>2.859</v>
       </c>
       <c r="M93">
-        <v>0.4540066440000001</v>
+        <v>0.458995728</v>
       </c>
       <c r="N93">
-        <v>2.404993356</v>
+        <v>2.400004272</v>
       </c>
       <c r="O93">
-        <v>0.3607490034</v>
+        <v>0.3600006408</v>
       </c>
       <c r="P93">
-        <v>2.0442443526</v>
+        <v>2.0400036312</v>
       </c>
       <c r="Q93">
-        <v>2.0752443526</v>
+        <v>2.0710036312</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7340388711052587</v>
+        <v>0.8187237350947594</v>
       </c>
       <c r="T93">
-        <v>8.970059674675326</v>
+        <v>10.07378734165188</v>
       </c>
       <c r="U93">
         <v>0.0543</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>6.297264671747842</v>
+        <v>6.228816142707105</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1079604988075807</v>
+        <v>0.1078564492156882</v>
       </c>
       <c r="C94">
-        <v>0.9216348865080111</v>
+        <v>0.8316241066373866</v>
       </c>
       <c r="D94">
-        <v>6.184594886508012</v>
+        <v>6.186464106637388</v>
       </c>
       <c r="E94">
-        <v>7.684960000000001</v>
+        <v>7.776840000000001</v>
       </c>
       <c r="F94">
-        <v>8.452960000000001</v>
+        <v>8.544840000000001</v>
       </c>
       <c r="G94">
         <v>3.19</v>
@@ -8989,28 +8989,28 @@
         <v>2.859</v>
       </c>
       <c r="M94">
-        <v>0.458995728</v>
+        <v>0.463984812</v>
       </c>
       <c r="N94">
-        <v>2.400004272</v>
+        <v>2.395015188</v>
       </c>
       <c r="O94">
-        <v>0.3600006408</v>
+        <v>0.3592522782</v>
       </c>
       <c r="P94">
-        <v>2.0400036312</v>
+        <v>2.0357629098</v>
       </c>
       <c r="Q94">
-        <v>2.0710036312</v>
+        <v>2.0667629098</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8187237350947594</v>
+        <v>0.9276042745098317</v>
       </c>
       <c r="T94">
-        <v>10.07378734165188</v>
+        <v>11.49286577062174</v>
       </c>
       <c r="U94">
         <v>0.0543</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>6.228816142707105</v>
+        <v>6.161839625043588</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1078564492156882</v>
+        <v>0.1085513996237956</v>
       </c>
       <c r="C95">
-        <v>0.8316241066373866</v>
+        <v>0.7272809137979994</v>
       </c>
       <c r="D95">
-        <v>6.186464106637388</v>
+        <v>6.174000913798</v>
       </c>
       <c r="E95">
-        <v>7.776840000000001</v>
+        <v>7.868720000000001</v>
       </c>
       <c r="F95">
-        <v>8.544840000000001</v>
+        <v>8.63672</v>
       </c>
       <c r="G95">
         <v>3.19</v>
@@ -9071,45 +9071,45 @@
         <v>2.859</v>
       </c>
       <c r="M95">
-        <v>0.463984812</v>
+        <v>0.477610616</v>
       </c>
       <c r="N95">
-        <v>2.395015188</v>
+        <v>2.381389384</v>
       </c>
       <c r="O95">
-        <v>0.3592522782</v>
+        <v>0.3572084075999999</v>
       </c>
       <c r="P95">
-        <v>2.0357629098</v>
+        <v>2.0241809764</v>
       </c>
       <c r="Q95">
-        <v>2.0667629098</v>
+        <v>2.0551809764</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9276042745098317</v>
+        <v>1.072778327063262</v>
       </c>
       <c r="T95">
-        <v>11.49286577062174</v>
+        <v>13.38497034258155</v>
       </c>
       <c r="U95">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V95">
         <v>0.15</v>
       </c>
       <c r="W95">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y95">
-        <v>6.161839625043588</v>
+        <v>5.986047847814169</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1085513996237956</v>
+        <v>0.1084558500319031</v>
       </c>
       <c r="C96">
-        <v>0.7272809137979994</v>
+        <v>0.6371115152648716</v>
       </c>
       <c r="D96">
-        <v>6.174000913798</v>
+        <v>6.175711515264874</v>
       </c>
       <c r="E96">
-        <v>7.868720000000001</v>
+        <v>7.960600000000002</v>
       </c>
       <c r="F96">
-        <v>8.63672</v>
+        <v>8.728600000000002</v>
       </c>
       <c r="G96">
         <v>3.19</v>
@@ -9153,28 +9153,28 @@
         <v>2.859</v>
       </c>
       <c r="M96">
-        <v>0.477610616</v>
+        <v>0.4826915800000001</v>
       </c>
       <c r="N96">
-        <v>2.381389384</v>
+        <v>2.37630842</v>
       </c>
       <c r="O96">
-        <v>0.3572084075999999</v>
+        <v>0.356446263</v>
       </c>
       <c r="P96">
-        <v>2.0241809764</v>
+        <v>2.019862157</v>
       </c>
       <c r="Q96">
-        <v>2.0551809764</v>
+        <v>2.050862157</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.072778327063262</v>
+        <v>1.276022000638064</v>
       </c>
       <c r="T96">
-        <v>13.38497034258155</v>
+        <v>16.03391674332528</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.986047847814169</v>
+        <v>5.923036817837177</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1084558500319031</v>
+        <v>0.1083603004400105</v>
       </c>
       <c r="C97">
-        <v>0.6371115152648716</v>
+        <v>0.546943064891094</v>
       </c>
       <c r="D97">
-        <v>6.175711515264874</v>
+        <v>6.177423064891096</v>
       </c>
       <c r="E97">
-        <v>7.960600000000002</v>
+        <v>8.052480000000001</v>
       </c>
       <c r="F97">
-        <v>8.728600000000002</v>
+        <v>8.820480000000002</v>
       </c>
       <c r="G97">
         <v>3.19</v>
@@ -9235,28 +9235,28 @@
         <v>2.859</v>
       </c>
       <c r="M97">
-        <v>0.4826915800000001</v>
+        <v>0.4877725440000001</v>
       </c>
       <c r="N97">
-        <v>2.37630842</v>
+        <v>2.371227456</v>
       </c>
       <c r="O97">
-        <v>0.356446263</v>
+        <v>0.3556841184</v>
       </c>
       <c r="P97">
-        <v>2.019862157</v>
+        <v>2.0155433376</v>
       </c>
       <c r="Q97">
-        <v>2.050862157</v>
+        <v>2.0465433376</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.276022000638064</v>
+        <v>1.580887511000267</v>
       </c>
       <c r="T97">
-        <v>16.03391674332528</v>
+        <v>20.00733634444088</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>5.923036817837177</v>
+        <v>5.861338517651373</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1083603004400105</v>
+        <v>0.108264750848118</v>
       </c>
       <c r="C98">
-        <v>0.5469430648910958</v>
+        <v>0.4567755634652109</v>
       </c>
       <c r="D98">
-        <v>6.177423064891096</v>
+        <v>6.17913556346521</v>
       </c>
       <c r="E98">
-        <v>8.052479999999999</v>
+        <v>8.144359999999999</v>
       </c>
       <c r="F98">
-        <v>8.82048</v>
+        <v>8.91236</v>
       </c>
       <c r="G98">
         <v>3.19</v>
@@ -9317,28 +9317,28 @@
         <v>2.859</v>
       </c>
       <c r="M98">
-        <v>0.487772544</v>
+        <v>0.492853508</v>
       </c>
       <c r="N98">
-        <v>2.371227456</v>
+        <v>2.366146492</v>
       </c>
       <c r="O98">
-        <v>0.3556841184</v>
+        <v>0.3549219738</v>
       </c>
       <c r="P98">
-        <v>2.0155433376</v>
+        <v>2.0112245182</v>
       </c>
       <c r="Q98">
-        <v>2.0465433376</v>
+        <v>2.0422245182</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.580887511000262</v>
+        <v>2.088996694937265</v>
       </c>
       <c r="T98">
-        <v>20.00733634444083</v>
+        <v>26.62970234630014</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>5.861338517651374</v>
+        <v>5.800912347366309</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.108264750848118</v>
+        <v>0.1081692012562255</v>
       </c>
       <c r="C99">
-        <v>0.4567755634652109</v>
+        <v>0.3666090117766316</v>
       </c>
       <c r="D99">
-        <v>6.17913556346521</v>
+        <v>6.180849011776632</v>
       </c>
       <c r="E99">
-        <v>8.144359999999999</v>
+        <v>8.23624</v>
       </c>
       <c r="F99">
-        <v>8.91236</v>
+        <v>9.004240000000001</v>
       </c>
       <c r="G99">
         <v>3.19</v>
@@ -9399,28 +9399,28 @@
         <v>2.859</v>
       </c>
       <c r="M99">
-        <v>0.492853508</v>
+        <v>0.4979344720000001</v>
       </c>
       <c r="N99">
-        <v>2.366146492</v>
+        <v>2.361065528</v>
       </c>
       <c r="O99">
-        <v>0.3549219738</v>
+        <v>0.3541598292</v>
       </c>
       <c r="P99">
-        <v>2.0112245182</v>
+        <v>2.0069056988</v>
       </c>
       <c r="Q99">
-        <v>2.0422245182</v>
+        <v>2.0379056988</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.088996694937265</v>
+        <v>3.105215062811271</v>
       </c>
       <c r="T99">
-        <v>26.62970234630014</v>
+        <v>39.87443435001876</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>5.800912347366309</v>
+        <v>5.741719364229918</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1081692012562255</v>
+        <v>0.1080736516643329</v>
       </c>
       <c r="C100">
-        <v>0.3666090117766316</v>
+        <v>0.2764434106156557</v>
       </c>
       <c r="D100">
-        <v>6.180849011776632</v>
+        <v>6.182563410615657</v>
       </c>
       <c r="E100">
-        <v>8.23624</v>
+        <v>8.32812</v>
       </c>
       <c r="F100">
-        <v>9.004240000000001</v>
+        <v>9.096120000000001</v>
       </c>
       <c r="G100">
         <v>3.19</v>
@@ -9481,28 +9481,28 @@
         <v>2.859</v>
       </c>
       <c r="M100">
-        <v>0.4979344720000001</v>
+        <v>0.5030154360000001</v>
       </c>
       <c r="N100">
-        <v>2.361065528</v>
+        <v>2.355984564</v>
       </c>
       <c r="O100">
-        <v>0.3541598292</v>
+        <v>0.3533976846</v>
       </c>
       <c r="P100">
-        <v>2.0069056988</v>
+        <v>2.0025868794</v>
       </c>
       <c r="Q100">
-        <v>2.0379056988</v>
+        <v>2.0335868794</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.105215062811271</v>
+        <v>6.153870166433288</v>
       </c>
       <c r="T100">
-        <v>39.87443435001876</v>
+        <v>79.60863036117462</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>5.741719364229918</v>
+        <v>5.683722198934666</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1080736516643329</v>
-      </c>
-      <c r="C101">
-        <v>0.2764434106156557</v>
-      </c>
-      <c r="D101">
-        <v>6.182563410615657</v>
-      </c>
-      <c r="E101">
-        <v>8.32812</v>
-      </c>
-      <c r="F101">
-        <v>9.096120000000001</v>
-      </c>
-      <c r="G101">
-        <v>3.19</v>
-      </c>
-      <c r="H101">
-        <v>8.42</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.89</v>
-      </c>
-      <c r="K101">
-        <v>0.031</v>
-      </c>
-      <c r="L101">
-        <v>2.859</v>
-      </c>
-      <c r="M101">
-        <v>0.5030154360000001</v>
-      </c>
-      <c r="N101">
-        <v>2.355984564</v>
-      </c>
-      <c r="O101">
-        <v>0.3533976846</v>
-      </c>
-      <c r="P101">
-        <v>2.0025868794</v>
-      </c>
-      <c r="Q101">
-        <v>2.0335868794</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.153870166433288</v>
-      </c>
-      <c r="T101">
-        <v>79.60863036117462</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.047005</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.683722198934666</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
